--- a/pages/ParaFactorTool/Para_4year_data_track.xlsx
+++ b/pages/ParaFactorTool/Para_4year_data_track.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\ParaFactorTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC53FACA-8D15-4CE2-8007-92B05A218994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61416962-E8D9-48FF-AEE2-E5EAC0A7BFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{398C2CAE-8513-48E9-A3F5-2A4019774188}"/>
+    <workbookView xWindow="38280" yWindow="7470" windowWidth="29040" windowHeight="15720" xr2:uid="{398C2CAE-8513-48E9-A3F5-2A4019774188}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -295,13 +295,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>152766</xdr:colOff>
-      <xdr:row>121</xdr:row>
+      <xdr:row>597</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>628650</xdr:colOff>
-      <xdr:row>1600</xdr:row>
+      <xdr:row>1593</xdr:row>
       <xdr:rowOff>144339</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -373,13 +373,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>86824</xdr:colOff>
-      <xdr:row>435</xdr:row>
+      <xdr:row>597</xdr:row>
       <xdr:rowOff>74734</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>630847</xdr:colOff>
-      <xdr:row>1601</xdr:row>
+      <xdr:row>1594</xdr:row>
       <xdr:rowOff>29674</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -451,13 +451,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>160093</xdr:colOff>
-      <xdr:row>1601</xdr:row>
+      <xdr:row>1594</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>635977</xdr:colOff>
-      <xdr:row>1614</xdr:row>
+      <xdr:row>1607</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -529,14 +529,14 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>106240</xdr:colOff>
-      <xdr:row>1601</xdr:row>
+      <xdr:row>1594</xdr:row>
       <xdr:rowOff>87191</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>732</xdr:colOff>
-      <xdr:row>1615</xdr:row>
-      <xdr:rowOff>46893</xdr:rowOff>
+      <xdr:row>1611</xdr:row>
+      <xdr:rowOff>29307</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -658,6 +658,14 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BD10C5AC-6F69-4783-B825-21587748049F}" name="Table2" displayName="Table2" ref="A1:G1592" totalsRowCount="1">
   <autoFilter ref="A1:G1591" xr:uid="{963A9C9A-A891-4AE2-AB26-5E2EF12B3783}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="2020"/>
+        <filter val="2022"/>
+        <filter val="2023"/>
+        <filter val="2024"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="1">
       <filters>
         <filter val="IP"/>
@@ -665,7 +673,7 @@
     </filterColumn>
     <filterColumn colId="2">
       <filters>
-        <filter val="C2"/>
+        <filter val="C5"/>
       </filters>
     </filterColumn>
     <filterColumn colId="3">
@@ -675,6 +683,8 @@
     </filterColumn>
     <filterColumn colId="4">
       <filters>
+        <filter val="1"/>
+        <filter val="2"/>
         <filter val="3"/>
       </filters>
     </filterColumn>
@@ -3762,7 +3772,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>2019</v>
       </c>
@@ -11007,7 +11017,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A436">
         <v>2020</v>
       </c>
@@ -14711,7 +14721,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="597" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="597" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A597">
         <v>2020</v>
       </c>
@@ -14734,7 +14744,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="598" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A598">
         <v>2020</v>
       </c>
@@ -14757,7 +14767,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="599" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A599">
         <v>2020</v>
       </c>
@@ -19112,7 +19122,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="788" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="788" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A788">
         <v>2022</v>
       </c>
@@ -20308,7 +20318,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="840" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="840" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A840">
         <v>2022</v>
       </c>
@@ -20331,7 +20341,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="841" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="841" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A841">
         <v>2022</v>
       </c>
@@ -20354,7 +20364,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="842" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="842" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A842">
         <v>2022</v>
       </c>
@@ -27714,7 +27724,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1162" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1162" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1162">
         <v>2023</v>
       </c>
@@ -28312,7 +28322,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1188" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1188" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1188">
         <v>2023</v>
       </c>
@@ -28335,7 +28345,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1189" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1189" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1189">
         <v>2023</v>
       </c>
@@ -28358,7 +28368,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1190" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1190" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1190">
         <v>2023</v>
       </c>
@@ -34890,7 +34900,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1474" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1474" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1474">
         <v>2024</v>
       </c>
@@ -37144,7 +37154,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1572" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1572" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1572">
         <v>2024</v>
       </c>
@@ -37167,7 +37177,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1573" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1573" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1573">
         <v>2024</v>
       </c>
@@ -37190,7 +37200,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1574" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1574" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1574">
         <v>2024</v>
       </c>
@@ -37624,48 +37634,53 @@
       </c>
       <c r="F1592">
         <f>SUBTOTAL(101,Table2[Time])</f>
-        <v>2.9932976474566311E-3</v>
+        <v>2.5896923225308646E-3</v>
       </c>
       <c r="G1592">
         <f>SUBTOTAL(101,Table2[Participants])</f>
-        <v>9</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="1593" spans="1:17" x14ac:dyDescent="0.45">
       <c r="F1593">
         <f>SUBTOTAL(107,Table2[Time])</f>
-        <v>9.1114024199937188E-5</v>
+        <v>5.846045836609146E-5</v>
       </c>
       <c r="G1593">
         <f>SUBTOTAL(107,Table2[Participants])</f>
-        <v>2.3452078799117149</v>
+        <v>4.266678503771459</v>
       </c>
     </row>
     <row r="1594" spans="1:17" x14ac:dyDescent="0.45">
       <c r="F1594">
-        <f>Table2[[#Totals],[Time]]*86400</f>
-        <v>258.62091674025294</v>
+        <f>Table2[[#Totals],[Time]]</f>
+        <v>2.5896923225308646E-3</v>
       </c>
       <c r="G1594">
         <f>SUBTOTAL(102,Table2[Participants])</f>
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1595" spans="1:17" x14ac:dyDescent="0.45">
       <c r="F1595">
         <f>F1593*86400</f>
-        <v>7.872251690874573</v>
+        <v>5.0509836028303026</v>
       </c>
       <c r="P1595">
         <v>4</v>
       </c>
     </row>
     <row r="1596" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="F1596" s="1">
+        <f>F1594</f>
+        <v>2.5896923225308646E-3</v>
+      </c>
       <c r="P1596">
         <v>0</v>
       </c>
     </row>
     <row r="1597" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="F1597" s="1"/>
       <c r="P1597">
         <v>0</v>
       </c>

--- a/pages/ParaFactorTool/Para_4year_data_track.xlsx
+++ b/pages/ParaFactorTool/Para_4year_data_track.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\ParaFactorTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61416962-E8D9-48FF-AEE2-E5EAC0A7BFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3248609-6969-46B8-967C-32AA43B3D7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="7470" windowWidth="29040" windowHeight="15720" xr2:uid="{398C2CAE-8513-48E9-A3F5-2A4019774188}"/>
+    <workbookView xWindow="25490" yWindow="15750" windowWidth="19420" windowHeight="10300" xr2:uid="{398C2CAE-8513-48E9-A3F5-2A4019774188}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -295,14 +295,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>152766</xdr:colOff>
-      <xdr:row>597</xdr:row>
+      <xdr:row>336</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>628650</xdr:colOff>
-      <xdr:row>1593</xdr:row>
-      <xdr:rowOff>144339</xdr:rowOff>
+      <xdr:row>1147</xdr:row>
+      <xdr:rowOff>144336</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -372,15 +372,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>86824</xdr:colOff>
-      <xdr:row>597</xdr:row>
+      <xdr:colOff>86821</xdr:colOff>
+      <xdr:row>336</xdr:row>
       <xdr:rowOff>74734</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>630847</xdr:colOff>
-      <xdr:row>1594</xdr:row>
-      <xdr:rowOff>29674</xdr:rowOff>
+      <xdr:row>1148</xdr:row>
+      <xdr:rowOff>29671</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -450,14 +450,14 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>160093</xdr:colOff>
-      <xdr:row>1594</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>164853</xdr:colOff>
+      <xdr:row>1148</xdr:row>
+      <xdr:rowOff>33335</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>635977</xdr:colOff>
-      <xdr:row>1607</xdr:row>
+      <xdr:colOff>640737</xdr:colOff>
+      <xdr:row>1595</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -528,15 +528,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>106240</xdr:colOff>
-      <xdr:row>1594</xdr:row>
-      <xdr:rowOff>87191</xdr:rowOff>
+      <xdr:colOff>106237</xdr:colOff>
+      <xdr:row>1148</xdr:row>
+      <xdr:rowOff>87188</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>732</xdr:colOff>
-      <xdr:row>1611</xdr:row>
-      <xdr:rowOff>29307</xdr:rowOff>
+      <xdr:row>1599</xdr:row>
+      <xdr:rowOff>34067</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -673,7 +673,7 @@
     </filterColumn>
     <filterColumn colId="2">
       <filters>
-        <filter val="C5"/>
+        <filter val="B"/>
       </filters>
     </filterColumn>
     <filterColumn colId="3">
@@ -686,6 +686,9 @@
         <filter val="1"/>
         <filter val="2"/>
         <filter val="3"/>
+        <filter val="4"/>
+        <filter val="5"/>
+        <filter val="6"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -8717,7 +8720,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A336">
         <v>2020</v>
       </c>
@@ -8740,7 +8743,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A337">
         <v>2020</v>
       </c>
@@ -8763,7 +8766,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A338">
         <v>2020</v>
       </c>
@@ -8786,7 +8789,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A339">
         <v>2020</v>
       </c>
@@ -8809,7 +8812,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A340">
         <v>2020</v>
       </c>
@@ -8832,7 +8835,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A341">
         <v>2020</v>
       </c>
@@ -14721,7 +14724,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="597" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="597" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A597">
         <v>2020</v>
       </c>
@@ -14744,7 +14747,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="598" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A598">
         <v>2020</v>
       </c>
@@ -14767,7 +14770,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="599" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A599">
         <v>2020</v>
       </c>
@@ -18386,7 +18389,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="756" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="756" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A756">
         <v>2022</v>
       </c>
@@ -18409,7 +18412,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="757" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="757" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A757">
         <v>2022</v>
       </c>
@@ -18432,7 +18435,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="758" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="758" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A758">
         <v>2022</v>
       </c>
@@ -18455,7 +18458,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="759" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="759" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A759">
         <v>2022</v>
       </c>
@@ -18478,7 +18481,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="760" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="760" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A760">
         <v>2022</v>
       </c>
@@ -18501,7 +18504,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="761" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="761" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A761">
         <v>2022</v>
       </c>
@@ -20318,7 +20321,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="840" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="840" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A840">
         <v>2022</v>
       </c>
@@ -20341,7 +20344,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="841" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="841" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A841">
         <v>2022</v>
       </c>
@@ -20364,7 +20367,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="842" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="842" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A842">
         <v>2022</v>
       </c>
@@ -27356,7 +27359,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1146" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1146" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1146">
         <v>2023</v>
       </c>
@@ -27379,7 +27382,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1147" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1147" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1147">
         <v>2023</v>
       </c>
@@ -27402,7 +27405,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1148" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1148" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1148">
         <v>2023</v>
       </c>
@@ -27425,7 +27428,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1149" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1149" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1149">
         <v>2023</v>
       </c>
@@ -27448,7 +27451,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1150" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1150" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1150">
         <v>2023</v>
       </c>
@@ -27471,7 +27474,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1151" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1151" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1151">
         <v>2023</v>
       </c>
@@ -28322,7 +28325,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1188" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1188" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1188">
         <v>2023</v>
       </c>
@@ -28345,7 +28348,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1189" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1189" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1189">
         <v>2023</v>
       </c>
@@ -28368,7 +28371,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1190" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1190" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1190">
         <v>2023</v>
       </c>
@@ -34302,7 +34305,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1448" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1448" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1448">
         <v>2024</v>
       </c>
@@ -34325,7 +34328,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1449" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1449" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1449">
         <v>2024</v>
       </c>
@@ -34348,7 +34351,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1450" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1450" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1450">
         <v>2024</v>
       </c>
@@ -34371,7 +34374,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1451" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1451" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1451">
         <v>2024</v>
       </c>
@@ -34394,7 +34397,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1452" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1452" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1452">
         <v>2024</v>
       </c>
@@ -34417,7 +34420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1453" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1453" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1453">
         <v>2024</v>
       </c>
@@ -37154,7 +37157,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1572" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="1572" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1572">
         <v>2024</v>
       </c>
@@ -37177,7 +37180,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1573" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="1573" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1573">
         <v>2024</v>
       </c>
@@ -37200,7 +37203,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1574" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="1574" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1574">
         <v>2024</v>
       </c>
@@ -37634,7 +37637,7 @@
       </c>
       <c r="F1592">
         <f>SUBTOTAL(101,Table2[Time])</f>
-        <v>2.5896923225308646E-3</v>
+        <v>2.4471952160493829E-3</v>
       </c>
       <c r="G1592">
         <f>SUBTOTAL(101,Table2[Participants])</f>
@@ -37644,27 +37647,27 @@
     <row r="1593" spans="1:17" x14ac:dyDescent="0.45">
       <c r="F1593">
         <f>SUBTOTAL(107,Table2[Time])</f>
-        <v>5.846045836609146E-5</v>
+        <v>1.0041578200526479E-4</v>
       </c>
       <c r="G1593">
         <f>SUBTOTAL(107,Table2[Participants])</f>
-        <v>4.266678503771459</v>
+        <v>1.5108304655560048</v>
       </c>
     </row>
     <row r="1594" spans="1:17" x14ac:dyDescent="0.45">
       <c r="F1594">
         <f>Table2[[#Totals],[Time]]</f>
-        <v>2.5896923225308646E-3</v>
+        <v>2.4471952160493829E-3</v>
       </c>
       <c r="G1594">
         <f>SUBTOTAL(102,Table2[Participants])</f>
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1595" spans="1:17" x14ac:dyDescent="0.45">
       <c r="F1595">
         <f>F1593*86400</f>
-        <v>5.0509836028303026</v>
+        <v>8.6759235652548785</v>
       </c>
       <c r="P1595">
         <v>4</v>
@@ -37673,7 +37676,7 @@
     <row r="1596" spans="1:17" x14ac:dyDescent="0.45">
       <c r="F1596" s="1">
         <f>F1594</f>
-        <v>2.5896923225308646E-3</v>
+        <v>2.4471952160493829E-3</v>
       </c>
       <c r="P1596">
         <v>0</v>

--- a/pages/ParaFactorTool/Para_4year_data_track.xlsx
+++ b/pages/ParaFactorTool/Para_4year_data_track.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\ParaFactorTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3248609-6969-46B8-967C-32AA43B3D7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B7EDEC-30CE-4DD7-A1AF-03B34C48F2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="15750" windowWidth="19420" windowHeight="10300" xr2:uid="{398C2CAE-8513-48E9-A3F5-2A4019774188}"/>
+    <workbookView xWindow="38280" yWindow="30" windowWidth="29040" windowHeight="15720" xr2:uid="{398C2CAE-8513-48E9-A3F5-2A4019774188}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -295,13 +295,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>152766</xdr:colOff>
-      <xdr:row>336</xdr:row>
+      <xdr:row>276</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>628650</xdr:colOff>
-      <xdr:row>1147</xdr:row>
+      <xdr:row>1600</xdr:row>
       <xdr:rowOff>144336</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -373,13 +373,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>86821</xdr:colOff>
-      <xdr:row>336</xdr:row>
+      <xdr:row>588</xdr:row>
       <xdr:rowOff>74734</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>630847</xdr:colOff>
-      <xdr:row>1148</xdr:row>
+      <xdr:row>1601</xdr:row>
       <xdr:rowOff>29671</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -450,14 +450,14 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>164853</xdr:colOff>
-      <xdr:row>1148</xdr:row>
-      <xdr:rowOff>33335</xdr:rowOff>
+      <xdr:colOff>169615</xdr:colOff>
+      <xdr:row>1601</xdr:row>
+      <xdr:rowOff>38097</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>640737</xdr:colOff>
-      <xdr:row>1595</xdr:row>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>730</xdr:colOff>
+      <xdr:row>1614</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -529,14 +529,14 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>106237</xdr:colOff>
-      <xdr:row>1148</xdr:row>
+      <xdr:row>1601</xdr:row>
       <xdr:rowOff>87188</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>732</xdr:colOff>
-      <xdr:row>1599</xdr:row>
-      <xdr:rowOff>34067</xdr:rowOff>
+      <xdr:row>1618</xdr:row>
+      <xdr:rowOff>38829</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
       <mc:Choice Requires="sle15">
@@ -658,22 +658,14 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BD10C5AC-6F69-4783-B825-21587748049F}" name="Table2" displayName="Table2" ref="A1:G1592" totalsRowCount="1">
   <autoFilter ref="A1:G1591" xr:uid="{963A9C9A-A891-4AE2-AB26-5E2EF12B3783}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="2020"/>
-        <filter val="2022"/>
-        <filter val="2023"/>
-        <filter val="2024"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="IP"/>
+        <filter val="500m"/>
       </filters>
     </filterColumn>
     <filterColumn colId="2">
       <filters>
-        <filter val="B"/>
+        <filter val="C5"/>
       </filters>
     </filterColumn>
     <filterColumn colId="3">
@@ -684,11 +676,6 @@
     <filterColumn colId="4">
       <filters>
         <filter val="1"/>
-        <filter val="2"/>
-        <filter val="3"/>
-        <filter val="4"/>
-        <filter val="5"/>
-        <filter val="6"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -7340,7 +7327,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A276">
         <v>2019</v>
       </c>
@@ -8720,7 +8707,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A336">
         <v>2020</v>
       </c>
@@ -8743,7 +8730,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A337">
         <v>2020</v>
       </c>
@@ -8766,7 +8753,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A338">
         <v>2020</v>
       </c>
@@ -8789,7 +8776,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A339">
         <v>2020</v>
       </c>
@@ -8812,7 +8799,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A340">
         <v>2020</v>
       </c>
@@ -8835,7 +8822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A341">
         <v>2020</v>
       </c>
@@ -14539,7 +14526,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="589" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A589">
         <v>2020</v>
       </c>
@@ -18159,7 +18146,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="746" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="746" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A746">
         <v>2022</v>
       </c>
@@ -18389,7 +18376,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="756" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="756" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A756">
         <v>2022</v>
       </c>
@@ -18412,7 +18399,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="757" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="757" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A757">
         <v>2022</v>
       </c>
@@ -18435,7 +18422,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="758" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="758" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A758">
         <v>2022</v>
       </c>
@@ -18458,7 +18445,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="759" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="759" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A759">
         <v>2022</v>
       </c>
@@ -18481,7 +18468,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="760" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="760" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A760">
         <v>2022</v>
       </c>
@@ -18504,7 +18491,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="761" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="761" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A761">
         <v>2022</v>
       </c>
@@ -25749,7 +25736,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1076" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1076" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1076">
         <v>2023</v>
       </c>
@@ -27359,7 +27346,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1146" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1146" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1146">
         <v>2023</v>
       </c>
@@ -27382,7 +27369,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1147" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1147" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1147">
         <v>2023</v>
       </c>
@@ -27405,7 +27392,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1148" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1148" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1148">
         <v>2023</v>
       </c>
@@ -27428,7 +27415,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1149" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1149" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1149">
         <v>2023</v>
       </c>
@@ -27451,7 +27438,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1150" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1150" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1150">
         <v>2023</v>
       </c>
@@ -27474,7 +27461,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1151" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1151" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1151">
         <v>2023</v>
       </c>
@@ -34305,7 +34292,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1448" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1448" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1448">
         <v>2024</v>
       </c>
@@ -34328,7 +34315,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1449" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1449" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1449">
         <v>2024</v>
       </c>
@@ -34351,7 +34338,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1450" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1450" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1450">
         <v>2024</v>
       </c>
@@ -34374,7 +34361,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1451" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1451" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1451">
         <v>2024</v>
       </c>
@@ -34397,7 +34384,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1452" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1452" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1452">
         <v>2024</v>
       </c>
@@ -34420,7 +34407,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1453" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1453" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1453">
         <v>2024</v>
       </c>
@@ -36697,7 +36684,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1552" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1552" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1552">
         <v>2024</v>
       </c>
@@ -37637,37 +37624,37 @@
       </c>
       <c r="F1592">
         <f>SUBTOTAL(101,Table2[Time])</f>
-        <v>2.4471952160493829E-3</v>
+        <v>36.577999999999996</v>
       </c>
       <c r="G1592">
         <f>SUBTOTAL(101,Table2[Participants])</f>
-        <v>13.25</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="1593" spans="1:17" x14ac:dyDescent="0.45">
       <c r="F1593">
         <f>SUBTOTAL(107,Table2[Time])</f>
-        <v>1.0041578200526479E-4</v>
+        <v>0.33617480571869235</v>
       </c>
       <c r="G1593">
         <f>SUBTOTAL(107,Table2[Participants])</f>
-        <v>1.5108304655560048</v>
+        <v>2.5884358211089546</v>
       </c>
     </row>
     <row r="1594" spans="1:17" x14ac:dyDescent="0.45">
       <c r="F1594">
         <f>Table2[[#Totals],[Time]]</f>
-        <v>2.4471952160493829E-3</v>
+        <v>36.577999999999996</v>
       </c>
       <c r="G1594">
         <f>SUBTOTAL(102,Table2[Participants])</f>
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1595" spans="1:17" x14ac:dyDescent="0.45">
       <c r="F1595">
         <f>F1593*86400</f>
-        <v>8.6759235652548785</v>
+        <v>29045.503214095021</v>
       </c>
       <c r="P1595">
         <v>4</v>
@@ -37676,7 +37663,7 @@
     <row r="1596" spans="1:17" x14ac:dyDescent="0.45">
       <c r="F1596" s="1">
         <f>F1594</f>
-        <v>2.4471952160493829E-3</v>
+        <v>36.577999999999996</v>
       </c>
       <c r="P1596">
         <v>0</v>

--- a/pages/ParaFactorTool/Para_4year_data_track.xlsx
+++ b/pages/ParaFactorTool/Para_4year_data_track.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\ParaFactorTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B7EDEC-30CE-4DD7-A1AF-03B34C48F2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D036FB7-1679-46A5-BC64-7CC17D4B3CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="30" windowWidth="29040" windowHeight="15720" xr2:uid="{398C2CAE-8513-48E9-A3F5-2A4019774188}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{398C2CAE-8513-48E9-A3F5-2A4019774188}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$1591</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$1786</definedName>
     <definedName name="Slicer_Class">#N/A</definedName>
     <definedName name="Slicer_Event">#N/A</definedName>
     <definedName name="Slicer_Rank">#N/A</definedName>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4778" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5362" uniqueCount="19">
   <si>
     <t>Year</t>
   </si>
@@ -112,16 +112,15 @@
   <si>
     <t>Participants</t>
   </si>
-  <si>
-    <t>Total</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mm:ss.000"/>
+    <numFmt numFmtId="173" formatCode="0.000"/>
+    <numFmt numFmtId="174" formatCode="m:ss.000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -138,15 +137,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -154,15 +159,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -295,13 +313,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>152766</xdr:colOff>
-      <xdr:row>276</xdr:row>
+      <xdr:row>1736</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>628650</xdr:colOff>
-      <xdr:row>1600</xdr:row>
+      <xdr:row>1798</xdr:row>
       <xdr:rowOff>144336</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -373,13 +391,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>86821</xdr:colOff>
-      <xdr:row>588</xdr:row>
+      <xdr:row>1736</xdr:row>
       <xdr:rowOff>74734</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>630847</xdr:colOff>
-      <xdr:row>1601</xdr:row>
+      <xdr:row>1799</xdr:row>
       <xdr:rowOff>29671</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -451,13 +469,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>169615</xdr:colOff>
-      <xdr:row>1601</xdr:row>
+      <xdr:row>1799</xdr:row>
       <xdr:rowOff>38097</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>730</xdr:colOff>
-      <xdr:row>1614</xdr:row>
+      <xdr:row>1812</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -529,13 +547,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>106237</xdr:colOff>
-      <xdr:row>1601</xdr:row>
+      <xdr:row>1799</xdr:row>
       <xdr:rowOff>87188</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>732</xdr:colOff>
-      <xdr:row>1618</xdr:row>
+      <xdr:row>1816</xdr:row>
       <xdr:rowOff>38829</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -656,16 +674,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BD10C5AC-6F69-4783-B825-21587748049F}" name="Table2" displayName="Table2" ref="A1:G1592" totalsRowCount="1">
-  <autoFilter ref="A1:G1591" xr:uid="{963A9C9A-A891-4AE2-AB26-5E2EF12B3783}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BD10C5AC-6F69-4783-B825-21587748049F}" name="Table2" displayName="Table2" ref="A1:G1786" totalsRowShown="0">
+  <autoFilter ref="A1:G1786" xr:uid="{963A9C9A-A891-4AE2-AB26-5E2EF12B3783}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="2022"/>
+        <filter val="2023"/>
+        <filter val="2024"/>
+        <filter val="2025"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="500m"/>
+        <filter val="Kilo"/>
       </filters>
     </filterColumn>
     <filterColumn colId="2">
       <filters>
-        <filter val="C5"/>
+        <filter val="C1"/>
       </filters>
     </filterColumn>
     <filterColumn colId="3">
@@ -676,17 +702,21 @@
     <filterColumn colId="4">
       <filters>
         <filter val="1"/>
+        <filter val="2"/>
+        <filter val="3"/>
+        <filter val="4"/>
+        <filter val="5"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{B72E1822-DCE5-4025-8EB7-7A1F1ADC4928}" name="Year" totalsRowLabel="Total"/>
+    <tableColumn id="1" xr3:uid="{B72E1822-DCE5-4025-8EB7-7A1F1ADC4928}" name="Year"/>
     <tableColumn id="2" xr3:uid="{B701CB16-337B-4FD7-B375-3DB23AA2F069}" name="Event"/>
     <tableColumn id="3" xr3:uid="{6A0738BF-EB18-4C14-8369-03EA5927D197}" name="Class"/>
     <tableColumn id="4" xr3:uid="{9B34D095-156E-436C-95D8-A66C22E64416}" name="Sex"/>
     <tableColumn id="5" xr3:uid="{913130A9-EA80-4376-B771-805DC532B8F1}" name="Rank"/>
-    <tableColumn id="6" xr3:uid="{6833436A-6E62-49C6-9833-A7CFB575AA67}" name="Time" totalsRowFunction="average" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{D30E61A1-A654-4C07-B50C-C93493F03A58}" name="Participants" totalsRowFunction="average"/>
+    <tableColumn id="6" xr3:uid="{6833436A-6E62-49C6-9833-A7CFB575AA67}" name="Time" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{D30E61A1-A654-4C07-B50C-C93493F03A58}" name="Participants"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -989,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{963A9C9A-A891-4AE2-AB26-5E2EF12B3783}">
-  <dimension ref="A1:Q1601"/>
+  <dimension ref="A1:Q1789"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -7327,7 +7357,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A276">
         <v>2019</v>
       </c>
@@ -14526,7 +14556,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A589">
         <v>2020</v>
       </c>
@@ -18146,7 +18176,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="746" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="746" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A746">
         <v>2022</v>
       </c>
@@ -25736,7 +25766,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1076" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1076" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1076">
         <v>2023</v>
       </c>
@@ -36684,7 +36714,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1552" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1552" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1552">
         <v>2024</v>
       </c>
@@ -37075,7 +37105,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1569" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1569" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1569">
         <v>2024</v>
       </c>
@@ -37098,7 +37128,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1570" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1570" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1570">
         <v>2024</v>
       </c>
@@ -37121,7 +37151,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1571" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1571" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1571">
         <v>2024</v>
       </c>
@@ -37144,7 +37174,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1572" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1572" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1572">
         <v>2024</v>
       </c>
@@ -37167,7 +37197,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1573" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1573" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1573">
         <v>2024</v>
       </c>
@@ -37190,7 +37220,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1574" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1574" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1574">
         <v>2024</v>
       </c>
@@ -37213,7 +37243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1575" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1575" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1575">
         <v>2024</v>
       </c>
@@ -37236,7 +37266,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1576" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1576" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1576">
         <v>2024</v>
       </c>
@@ -37259,7 +37289,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1577" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1577" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1577">
         <v>2024</v>
       </c>
@@ -37282,7 +37312,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1578" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1578" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1578">
         <v>2024</v>
       </c>
@@ -37305,7 +37335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1579" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1579" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1579">
         <v>2024</v>
       </c>
@@ -37328,7 +37358,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1580" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1580" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1580">
         <v>2024</v>
       </c>
@@ -37351,7 +37381,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1581" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1581" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1581">
         <v>2024</v>
       </c>
@@ -37374,7 +37404,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1582" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1582" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1582">
         <v>2024</v>
       </c>
@@ -37396,11 +37426,8 @@
       <c r="G1582">
         <v>10</v>
       </c>
-      <c r="P1582">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1583" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="1583" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1583">
         <v>2024</v>
       </c>
@@ -37422,11 +37449,8 @@
       <c r="G1583">
         <v>10</v>
       </c>
-      <c r="P1583">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1584" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="1584" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1584">
         <v>2024</v>
       </c>
@@ -37447,10 +37471,6 @@
       </c>
       <c r="G1584">
         <v>10</v>
-      </c>
-      <c r="Q1584">
-        <f>AVERAGE(P1579:P1583)</f>
-        <v>5.5</v>
       </c>
     </row>
     <row r="1585" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
@@ -37475,10 +37495,6 @@
       <c r="G1585">
         <v>10</v>
       </c>
-      <c r="Q1585">
-        <f>_xlfn.STDEV.S(P1579:P1583)</f>
-        <v>7.7781745930520225</v>
-      </c>
     </row>
     <row r="1586" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1586">
@@ -37618,151 +37634,4602 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1592" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A1592" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1592">
-        <f>SUBTOTAL(101,Table2[Time])</f>
-        <v>36.577999999999996</v>
+    <row r="1592" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1592">
+        <v>2025</v>
+      </c>
+      <c r="B1592" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1592" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1592" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1592">
+        <v>1</v>
+      </c>
+      <c r="F1592" s="3">
+        <v>7.2025462962962961E-4</v>
       </c>
       <c r="G1592">
-        <f>SUBTOTAL(101,Table2[Participants])</f>
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="1593" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="F1593">
-        <f>SUBTOTAL(107,Table2[Time])</f>
-        <v>0.33617480571869235</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1593">
+        <v>2025</v>
+      </c>
+      <c r="B1593" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1593" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1593" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1593">
+        <v>2</v>
+      </c>
+      <c r="F1593" s="3">
+        <v>7.2217592592592591E-4</v>
       </c>
       <c r="G1593">
-        <f>SUBTOTAL(107,Table2[Participants])</f>
-        <v>2.5884358211089546</v>
-      </c>
-    </row>
-    <row r="1594" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="F1594">
-        <f>Table2[[#Totals],[Time]]</f>
-        <v>36.577999999999996</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1594">
+        <v>2025</v>
+      </c>
+      <c r="B1594" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1594" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1594" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1594">
+        <v>3</v>
+      </c>
+      <c r="F1594" s="3">
+        <v>7.270370370370371E-4</v>
       </c>
       <c r="G1594">
-        <f>SUBTOTAL(102,Table2[Participants])</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="1595" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="F1595">
-        <f>F1593*86400</f>
-        <v>29045.503214095021</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1595">
+        <v>2025</v>
+      </c>
+      <c r="B1595" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1595" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1595" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1595">
+        <v>4</v>
+      </c>
+      <c r="F1595" s="3">
+        <v>7.3109953703703705E-4</v>
+      </c>
+      <c r="G1595">
+        <v>12</v>
       </c>
       <c r="P1595">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="1596" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="F1596" s="1">
-        <f>F1594</f>
-        <v>36.577999999999996</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1596">
+        <v>2025</v>
+      </c>
+      <c r="B1596" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1596" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1596" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1596">
+        <v>5</v>
+      </c>
+      <c r="F1596" s="3">
+        <v>7.4450231481481481E-4</v>
+      </c>
+      <c r="G1596">
+        <v>12</v>
       </c>
       <c r="P1596">
         <v>0</v>
       </c>
     </row>
-    <row r="1597" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="F1597" s="1"/>
+    <row r="1597" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1597">
+        <v>2025</v>
+      </c>
+      <c r="B1597" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1597" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1597" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1597">
+        <v>6</v>
+      </c>
+      <c r="F1597" s="3">
+        <v>7.5658564814814816E-4</v>
+      </c>
+      <c r="G1597">
+        <v>12</v>
+      </c>
       <c r="P1597">
         <v>0</v>
       </c>
     </row>
-    <row r="1598" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="1598" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1598">
+        <v>2025</v>
+      </c>
+      <c r="B1598" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1598" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1598" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1598">
+        <v>7</v>
+      </c>
+      <c r="F1598" s="3">
+        <v>7.6048611111111119E-4</v>
+      </c>
+      <c r="G1598">
+        <v>12</v>
+      </c>
       <c r="P1598">
         <v>0</v>
       </c>
     </row>
-    <row r="1599" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="P1599">
+    <row r="1599" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1599">
+        <v>2025</v>
+      </c>
+      <c r="B1599" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1599" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1599" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1599">
+        <v>8</v>
+      </c>
+      <c r="F1599" s="3">
+        <v>7.6531250000000004E-4</v>
+      </c>
+      <c r="G1599">
+        <v>12</v>
+      </c>
+      <c r="Q1599">
+        <f>AVERAGE(P1595:P1598)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="1600" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="1600" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1600">
+        <v>2025</v>
+      </c>
+      <c r="B1600" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1600" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1600" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1600">
+        <v>9</v>
+      </c>
+      <c r="F1600" s="3">
+        <v>7.6857638888888895E-4</v>
+      </c>
+      <c r="G1600">
+        <v>12</v>
+      </c>
       <c r="Q1600">
-        <f>AVERAGE(P1595:P1599)</f>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="1601" spans="17:17" x14ac:dyDescent="0.45">
-      <c r="Q1601">
-        <f>_xlfn.STDEV.S(P1595:P1599)</f>
-        <v>1.7888543819998317</v>
+        <f>_xlfn.STDEV.S(P1595:P1598)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1601">
+        <v>2025</v>
+      </c>
+      <c r="B1601" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1601" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1601" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1601">
+        <v>10</v>
+      </c>
+      <c r="F1601" s="3">
+        <v>7.8284722222222232E-4</v>
+      </c>
+      <c r="G1601">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1602">
+        <v>2025</v>
+      </c>
+      <c r="B1602" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1602" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1602" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1602">
+        <v>1</v>
+      </c>
+      <c r="F1602" s="3">
+        <v>2.8302893518518521E-3</v>
+      </c>
+      <c r="G1602">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1603">
+        <v>2025</v>
+      </c>
+      <c r="B1603" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1603" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1603" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1603">
+        <v>2</v>
+      </c>
+      <c r="F1603" s="3">
+        <v>2.878912037037037E-3</v>
+      </c>
+      <c r="G1603">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1604">
+        <v>2025</v>
+      </c>
+      <c r="B1604" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1604" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1604" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1604">
+        <v>3</v>
+      </c>
+      <c r="F1604" s="3">
+        <v>2.9370486111111112E-3</v>
+      </c>
+      <c r="G1604">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1605">
+        <v>2025</v>
+      </c>
+      <c r="B1605" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1605" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1605" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1605">
+        <v>4</v>
+      </c>
+      <c r="F1605" s="3">
+        <v>3.1300462962962961E-3</v>
+      </c>
+      <c r="G1605">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1606">
+        <v>2025</v>
+      </c>
+      <c r="B1606" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1606" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1606" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1606">
+        <v>5</v>
+      </c>
+      <c r="F1606" s="3">
+        <v>3.2075810185185185E-3</v>
+      </c>
+      <c r="G1606">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1607">
+        <v>2025</v>
+      </c>
+      <c r="B1607" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1607" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1607" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1607">
+        <v>6</v>
+      </c>
+      <c r="F1607" s="3">
+        <v>3.2195138888888889E-3</v>
+      </c>
+      <c r="G1607">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1608">
+        <v>2025</v>
+      </c>
+      <c r="B1608" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1608" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1608" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1608">
+        <v>7</v>
+      </c>
+      <c r="F1608" s="3">
+        <v>3.2763657407407403E-3</v>
+      </c>
+      <c r="G1608">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1609">
+        <v>2025</v>
+      </c>
+      <c r="B1609" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1609" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1609" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1609">
+        <v>8</v>
+      </c>
+      <c r="F1609" s="3">
+        <v>3.3892939814814814E-3</v>
+      </c>
+      <c r="G1609">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1610">
+        <v>2025</v>
+      </c>
+      <c r="B1610" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1610" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1610" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1610">
+        <v>9</v>
+      </c>
+      <c r="F1610" s="3">
+        <v>3.7602777777777773E-3</v>
+      </c>
+      <c r="G1610">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1611">
+        <v>2025</v>
+      </c>
+      <c r="B1611" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1611" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1611" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1611">
+        <v>1</v>
+      </c>
+      <c r="F1611">
+        <v>10.061</v>
+      </c>
+      <c r="G1611">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1612">
+        <v>2025</v>
+      </c>
+      <c r="B1612" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1612" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1612" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1612">
+        <v>2</v>
+      </c>
+      <c r="F1612">
+        <v>10.221</v>
+      </c>
+      <c r="G1612">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1613">
+        <v>2025</v>
+      </c>
+      <c r="B1613" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1613" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1613" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1613">
+        <v>3</v>
+      </c>
+      <c r="F1613">
+        <v>10.273999999999999</v>
+      </c>
+      <c r="G1613">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1614">
+        <v>2025</v>
+      </c>
+      <c r="B1614" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1614" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1614" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1614">
+        <v>4</v>
+      </c>
+      <c r="F1614">
+        <v>10.308999999999999</v>
+      </c>
+      <c r="G1614">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1615">
+        <v>2025</v>
+      </c>
+      <c r="B1615" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1615" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1615" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1615">
+        <v>5</v>
+      </c>
+      <c r="F1615">
+        <v>10.704000000000001</v>
+      </c>
+      <c r="G1615">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1616">
+        <v>2025</v>
+      </c>
+      <c r="B1616" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1616" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1616" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1616">
+        <v>6</v>
+      </c>
+      <c r="F1616">
+        <v>10.741</v>
+      </c>
+      <c r="G1616">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1617">
+        <v>2025</v>
+      </c>
+      <c r="B1617" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1617" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1617" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1617">
+        <v>7</v>
+      </c>
+      <c r="F1617">
+        <v>10.95</v>
+      </c>
+      <c r="G1617">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1618">
+        <v>2025</v>
+      </c>
+      <c r="B1618" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1618" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1618" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1618">
+        <v>8</v>
+      </c>
+      <c r="F1618">
+        <v>11.243</v>
+      </c>
+      <c r="G1618">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1619">
+        <v>2025</v>
+      </c>
+      <c r="B1619" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1619" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1619" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1619">
+        <v>9</v>
+      </c>
+      <c r="F1619">
+        <v>11.263</v>
+      </c>
+      <c r="G1619">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1620">
+        <v>2025</v>
+      </c>
+      <c r="B1620" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1620" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1620" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1620">
+        <v>10</v>
+      </c>
+      <c r="F1620">
+        <v>11.298999999999999</v>
+      </c>
+      <c r="G1620">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1621">
+        <v>2025</v>
+      </c>
+      <c r="B1621" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1621" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1621" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1621">
+        <v>1</v>
+      </c>
+      <c r="F1621" s="3">
+        <v>8.5783564814814815E-4</v>
+      </c>
+      <c r="G1621">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1622">
+        <v>2025</v>
+      </c>
+      <c r="B1622" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1622" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1622" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1622">
+        <v>2</v>
+      </c>
+      <c r="F1622" s="3">
+        <v>8.8890046296296297E-4</v>
+      </c>
+      <c r="G1622">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1623">
+        <v>2025</v>
+      </c>
+      <c r="B1623" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1623" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1623" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1623">
+        <v>3</v>
+      </c>
+      <c r="F1623" s="3">
+        <v>9.3841435185185195E-4</v>
+      </c>
+      <c r="G1623">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1624">
+        <v>2025</v>
+      </c>
+      <c r="B1624" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1624" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1624" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1624">
+        <v>4</v>
+      </c>
+      <c r="F1624" s="3">
+        <v>9.6688657407407411E-4</v>
+      </c>
+      <c r="G1624">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1625">
+        <v>2025</v>
+      </c>
+      <c r="B1625" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1625" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1625" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1625">
+        <v>5</v>
+      </c>
+      <c r="F1625" s="3">
+        <v>9.917129629629629E-4</v>
+      </c>
+      <c r="G1625">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1626">
+        <v>2025</v>
+      </c>
+      <c r="B1626" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1626" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1626" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1626">
+        <v>6</v>
+      </c>
+      <c r="F1626" s="3">
+        <v>9.9526620370370372E-4</v>
+      </c>
+      <c r="G1626">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1627">
+        <v>2025</v>
+      </c>
+      <c r="B1627" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1627" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1627" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1627">
+        <v>7</v>
+      </c>
+      <c r="F1627" s="3">
+        <v>1.167523148148148E-3</v>
+      </c>
+      <c r="G1627">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1628">
+        <v>2025</v>
+      </c>
+      <c r="B1628" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1628" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1628" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1628">
+        <v>1</v>
+      </c>
+      <c r="F1628">
+        <v>12.249000000000001</v>
+      </c>
+      <c r="G1628">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1629">
+        <v>2025</v>
+      </c>
+      <c r="B1629" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1629" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1629" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1629">
+        <v>2</v>
+      </c>
+      <c r="F1629">
+        <v>13.151999999999999</v>
+      </c>
+      <c r="G1629">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1630">
+        <v>2025</v>
+      </c>
+      <c r="B1630" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1630" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1630" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1630">
+        <v>3</v>
+      </c>
+      <c r="F1630">
+        <v>13.173999999999999</v>
+      </c>
+      <c r="G1630">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1631">
+        <v>2025</v>
+      </c>
+      <c r="B1631" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1631" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1631" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1631">
+        <v>4</v>
+      </c>
+      <c r="F1631">
+        <v>13.773999999999999</v>
+      </c>
+      <c r="G1631">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1632">
+        <v>2025</v>
+      </c>
+      <c r="B1632" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1632" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1632" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1632">
+        <v>5</v>
+      </c>
+      <c r="F1632">
+        <v>14.271000000000001</v>
+      </c>
+      <c r="G1632">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1633">
+        <v>2025</v>
+      </c>
+      <c r="B1633" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1633" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1633" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1633">
+        <v>6</v>
+      </c>
+      <c r="F1633">
+        <v>14.436</v>
+      </c>
+      <c r="G1633">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1634">
+        <v>2025</v>
+      </c>
+      <c r="B1634" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1634" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1634" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1634">
+        <v>7</v>
+      </c>
+      <c r="F1634">
+        <v>14.651999999999999</v>
+      </c>
+      <c r="G1634">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1635">
+        <v>2025</v>
+      </c>
+      <c r="B1635" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1635" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1635" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1635">
+        <v>8</v>
+      </c>
+      <c r="F1635">
+        <v>16.608000000000001</v>
+      </c>
+      <c r="G1635">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1636">
+        <v>2025</v>
+      </c>
+      <c r="B1636" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1636" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1636" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1636">
+        <v>1</v>
+      </c>
+      <c r="F1636" s="3">
+        <v>7.8971064814814811E-4</v>
+      </c>
+      <c r="G1636">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1637">
+        <v>2025</v>
+      </c>
+      <c r="B1637" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1637" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1637" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1637">
+        <v>2</v>
+      </c>
+      <c r="F1637" s="3">
+        <v>8.1380787037037044E-4</v>
+      </c>
+      <c r="G1637">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1638">
+        <v>2025</v>
+      </c>
+      <c r="B1638" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1638" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1638" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1638">
+        <v>3</v>
+      </c>
+      <c r="F1638" s="3">
+        <v>8.178472222222223E-4</v>
+      </c>
+      <c r="G1638">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1639">
+        <v>2025</v>
+      </c>
+      <c r="B1639" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1639" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1639" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1639">
+        <v>4</v>
+      </c>
+      <c r="F1639" s="3">
+        <v>8.2194444444444448E-4</v>
+      </c>
+      <c r="G1639">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1640">
+        <v>2025</v>
+      </c>
+      <c r="B1640" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1640" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1640" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1640">
+        <v>5</v>
+      </c>
+      <c r="F1640" s="3">
+        <v>8.3988425925925929E-4</v>
+      </c>
+      <c r="G1640">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1641">
+        <v>2025</v>
+      </c>
+      <c r="B1641" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1641" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1641" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1641">
+        <v>6</v>
+      </c>
+      <c r="F1641" s="3">
+        <v>8.7141203703703697E-4</v>
+      </c>
+      <c r="G1641">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1642">
+        <v>2025</v>
+      </c>
+      <c r="B1642" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1642" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1642" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1642">
+        <v>7</v>
+      </c>
+      <c r="F1642" s="3">
+        <v>8.7350694444444444E-4</v>
+      </c>
+      <c r="G1642">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1643">
+        <v>2025</v>
+      </c>
+      <c r="B1643" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1643" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1643" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1643">
+        <v>8</v>
+      </c>
+      <c r="F1643" s="3">
+        <v>8.9267361111111101E-4</v>
+      </c>
+      <c r="G1643">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1644">
+        <v>2025</v>
+      </c>
+      <c r="B1644" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1644" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1644" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1644">
+        <v>9</v>
+      </c>
+      <c r="F1644" s="3">
+        <v>9.4520833333333327E-4</v>
+      </c>
+      <c r="G1644">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1645">
+        <v>2025</v>
+      </c>
+      <c r="B1645" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1645" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1645" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1645">
+        <v>10</v>
+      </c>
+      <c r="F1645" s="3">
+        <v>1.0028125E-3</v>
+      </c>
+      <c r="G1645">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1646">
+        <v>2025</v>
+      </c>
+      <c r="B1646" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1646" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1646" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1646">
+        <v>1</v>
+      </c>
+      <c r="F1646">
+        <v>11.336</v>
+      </c>
+      <c r="G1646">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1647">
+        <v>2025</v>
+      </c>
+      <c r="B1647" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1647" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1647" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1647">
+        <v>2</v>
+      </c>
+      <c r="F1647">
+        <v>11.488</v>
+      </c>
+      <c r="G1647">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1648">
+        <v>2025</v>
+      </c>
+      <c r="B1648" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1648" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1648" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1648">
+        <v>3</v>
+      </c>
+      <c r="F1648">
+        <v>11.643000000000001</v>
+      </c>
+      <c r="G1648">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1649">
+        <v>2025</v>
+      </c>
+      <c r="B1649" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1649" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1649" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1649">
+        <v>4</v>
+      </c>
+      <c r="F1649">
+        <v>11.686999999999999</v>
+      </c>
+      <c r="G1649">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1650">
+        <v>2025</v>
+      </c>
+      <c r="B1650" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1650" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1650" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1650">
+        <v>5</v>
+      </c>
+      <c r="F1650">
+        <v>11.75</v>
+      </c>
+      <c r="G1650">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1651">
+        <v>2025</v>
+      </c>
+      <c r="B1651" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1651" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1651" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1651">
+        <v>6</v>
+      </c>
+      <c r="F1651">
+        <v>12.552</v>
+      </c>
+      <c r="G1651">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1652">
+        <v>2025</v>
+      </c>
+      <c r="B1652" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1652" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1652" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1652">
+        <v>7</v>
+      </c>
+      <c r="F1652">
+        <v>12.584</v>
+      </c>
+      <c r="G1652">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1653">
+        <v>2025</v>
+      </c>
+      <c r="B1653" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1653" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1653" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1653">
+        <v>8</v>
+      </c>
+      <c r="F1653">
+        <v>13.279</v>
+      </c>
+      <c r="G1653">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1654">
+        <v>2025</v>
+      </c>
+      <c r="B1654" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1654" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1654" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1654">
+        <v>9</v>
+      </c>
+      <c r="F1654">
+        <v>13.298</v>
+      </c>
+      <c r="G1654">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1655">
+        <v>2025</v>
+      </c>
+      <c r="B1655" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1655" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1655" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1655">
+        <v>10</v>
+      </c>
+      <c r="F1655">
+        <v>13.641</v>
+      </c>
+      <c r="G1655">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1656">
+        <v>2025</v>
+      </c>
+      <c r="B1656" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1656" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1656" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1656">
+        <v>1</v>
+      </c>
+      <c r="F1656" s="3">
+        <v>7.2740740740740741E-4</v>
+      </c>
+      <c r="G1656">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1657">
+        <v>2025</v>
+      </c>
+      <c r="B1657" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1657" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1657" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1657">
+        <v>2</v>
+      </c>
+      <c r="F1657" s="3">
+        <v>7.6706018518518518E-4</v>
+      </c>
+      <c r="G1657">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1658">
+        <v>2025</v>
+      </c>
+      <c r="B1658" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1658" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1658" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1658">
+        <v>3</v>
+      </c>
+      <c r="F1658" s="3">
+        <v>7.9138888888888889E-4</v>
+      </c>
+      <c r="G1658">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1659">
+        <v>2025</v>
+      </c>
+      <c r="B1659" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1659" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1659" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1659">
+        <v>4</v>
+      </c>
+      <c r="F1659" s="3">
+        <v>8.0052083333333321E-4</v>
+      </c>
+      <c r="G1659">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1660">
+        <v>2025</v>
+      </c>
+      <c r="B1660" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1660" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1660" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1660">
+        <v>5</v>
+      </c>
+      <c r="F1660" s="3">
+        <v>9.2939814814814816E-4</v>
+      </c>
+      <c r="G1660">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1661">
+        <v>2025</v>
+      </c>
+      <c r="B1661" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1661" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1661" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1661">
+        <v>1</v>
+      </c>
+      <c r="F1661">
+        <v>10.581</v>
+      </c>
+      <c r="G1661">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1662">
+        <v>2025</v>
+      </c>
+      <c r="B1662" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1662" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1662" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1662">
+        <v>2</v>
+      </c>
+      <c r="F1662">
+        <v>10.792999999999999</v>
+      </c>
+      <c r="G1662">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1663">
+        <v>2025</v>
+      </c>
+      <c r="B1663" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1663" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1663" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1663">
+        <v>3</v>
+      </c>
+      <c r="F1663">
+        <v>11.595000000000001</v>
+      </c>
+      <c r="G1663">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1664">
+        <v>2025</v>
+      </c>
+      <c r="B1664" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1664" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1664" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1664">
+        <v>4</v>
+      </c>
+      <c r="F1664">
+        <v>11.896000000000001</v>
+      </c>
+      <c r="G1664">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1665">
+        <v>2025</v>
+      </c>
+      <c r="B1665" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1665" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1665" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1665">
+        <v>5</v>
+      </c>
+      <c r="F1665">
+        <v>11.975</v>
+      </c>
+      <c r="G1665">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1666">
+        <v>2025</v>
+      </c>
+      <c r="B1666" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1666" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1666" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1666">
+        <v>6</v>
+      </c>
+      <c r="F1666">
+        <v>13.724</v>
+      </c>
+      <c r="G1666">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1667">
+        <v>2025</v>
+      </c>
+      <c r="B1667" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1667" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1667" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1667">
+        <v>1</v>
+      </c>
+      <c r="F1667" s="3">
+        <v>7.5105324074074083E-4</v>
+      </c>
+      <c r="G1667">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1668">
+        <v>2025</v>
+      </c>
+      <c r="B1668" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1668" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1668" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1668">
+        <v>2</v>
+      </c>
+      <c r="F1668" s="3">
+        <v>7.5303240740740734E-4</v>
+      </c>
+      <c r="G1668">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1669">
+        <v>2025</v>
+      </c>
+      <c r="B1669" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1669" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1669" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1669">
+        <v>3</v>
+      </c>
+      <c r="F1669" s="3">
+        <v>7.5658564814814816E-4</v>
+      </c>
+      <c r="G1669">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1670">
+        <v>2025</v>
+      </c>
+      <c r="B1670" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1670" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1670" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1670">
+        <v>4</v>
+      </c>
+      <c r="F1670" s="3">
+        <v>7.6138888888888892E-4</v>
+      </c>
+      <c r="G1670">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1671">
+        <v>2025</v>
+      </c>
+      <c r="B1671" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1671" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1671" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1671">
+        <v>5</v>
+      </c>
+      <c r="F1671" s="3">
+        <v>7.9449074074074079E-4</v>
+      </c>
+      <c r="G1671">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1672">
+        <v>2025</v>
+      </c>
+      <c r="B1672" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1672" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1672" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1672">
+        <v>6</v>
+      </c>
+      <c r="F1672" s="3">
+        <v>8.0921296296296297E-4</v>
+      </c>
+      <c r="G1672">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1673">
+        <v>2025</v>
+      </c>
+      <c r="B1673" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1673" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1673" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1673">
+        <v>7</v>
+      </c>
+      <c r="F1673" s="3">
+        <v>8.1747685185185178E-4</v>
+      </c>
+      <c r="G1673">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1674">
+        <v>2025</v>
+      </c>
+      <c r="B1674" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1674" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1674" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1674">
+        <v>8</v>
+      </c>
+      <c r="F1674" s="3">
+        <v>8.3724537037037025E-4</v>
+      </c>
+      <c r="G1674">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1675">
+        <v>2025</v>
+      </c>
+      <c r="B1675" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1675" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1675" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1675">
+        <v>9</v>
+      </c>
+      <c r="F1675" s="3">
+        <v>8.4259259259259259E-4</v>
+      </c>
+      <c r="G1675">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1676">
+        <v>2025</v>
+      </c>
+      <c r="B1676" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1676" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1676" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1676">
+        <v>10</v>
+      </c>
+      <c r="F1676" s="3">
+        <v>8.4907407407407403E-4</v>
+      </c>
+      <c r="G1676">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1677">
+        <v>2025</v>
+      </c>
+      <c r="B1677" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1677" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1677" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1677">
+        <v>1</v>
+      </c>
+      <c r="F1677">
+        <v>10.333</v>
+      </c>
+      <c r="G1677">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1678">
+        <v>2025</v>
+      </c>
+      <c r="B1678" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1678" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1678" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1678">
+        <v>2</v>
+      </c>
+      <c r="F1678">
+        <v>10.861000000000001</v>
+      </c>
+      <c r="G1678">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1679">
+        <v>2025</v>
+      </c>
+      <c r="B1679" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1679" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1679" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1679">
+        <v>3</v>
+      </c>
+      <c r="F1679">
+        <v>11.016999999999999</v>
+      </c>
+      <c r="G1679">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1680">
+        <v>2025</v>
+      </c>
+      <c r="B1680" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1680" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1680" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1680">
+        <v>4</v>
+      </c>
+      <c r="F1680">
+        <v>11.231999999999999</v>
+      </c>
+      <c r="G1680">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1681">
+        <v>2025</v>
+      </c>
+      <c r="B1681" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1681" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1681" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1681">
+        <v>5</v>
+      </c>
+      <c r="F1681">
+        <v>11.438000000000001</v>
+      </c>
+      <c r="G1681">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1682">
+        <v>2025</v>
+      </c>
+      <c r="B1682" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1682" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1682" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1682">
+        <v>6</v>
+      </c>
+      <c r="F1682">
+        <v>11.483000000000001</v>
+      </c>
+      <c r="G1682">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1683">
+        <v>2025</v>
+      </c>
+      <c r="B1683" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1683" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1683" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1683">
+        <v>7</v>
+      </c>
+      <c r="F1683">
+        <v>11.664</v>
+      </c>
+      <c r="G1683">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1684">
+        <v>2025</v>
+      </c>
+      <c r="B1684" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1684" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1684" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1684">
+        <v>8</v>
+      </c>
+      <c r="F1684">
+        <v>11.808999999999999</v>
+      </c>
+      <c r="G1684">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1685">
+        <v>2025</v>
+      </c>
+      <c r="B1685" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1685" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1685" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1685">
+        <v>9</v>
+      </c>
+      <c r="F1685">
+        <v>12.032</v>
+      </c>
+      <c r="G1685">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1686">
+        <v>2025</v>
+      </c>
+      <c r="B1686" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1686" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1686" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1686">
+        <v>10</v>
+      </c>
+      <c r="F1686">
+        <v>12.22</v>
+      </c>
+      <c r="G1686">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1687">
+        <v>2025</v>
+      </c>
+      <c r="B1687" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1687" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1687" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1687">
+        <v>1</v>
+      </c>
+      <c r="F1687" s="3">
+        <v>7.4114583333333324E-4</v>
+      </c>
+      <c r="G1687">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1688">
+        <v>2025</v>
+      </c>
+      <c r="B1688" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1688" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1688" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1688">
+        <v>2</v>
+      </c>
+      <c r="F1688" s="3">
+        <v>7.4767361111111117E-4</v>
+      </c>
+      <c r="G1688">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1689">
+        <v>2025</v>
+      </c>
+      <c r="B1689" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1689" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1689" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1689">
+        <v>3</v>
+      </c>
+      <c r="F1689" s="3">
+        <v>7.6137731481481488E-4</v>
+      </c>
+      <c r="G1689">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1690">
+        <v>2025</v>
+      </c>
+      <c r="B1690" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1690" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1690" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1690">
+        <v>4</v>
+      </c>
+      <c r="F1690" s="3">
+        <v>7.7320601851851856E-4</v>
+      </c>
+      <c r="G1690">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1691">
+        <v>2025</v>
+      </c>
+      <c r="B1691" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1691" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1691" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1691">
+        <v>5</v>
+      </c>
+      <c r="F1691" s="3">
+        <v>7.7756944444444445E-4</v>
+      </c>
+      <c r="G1691">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1692">
+        <v>2025</v>
+      </c>
+      <c r="B1692" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1692" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1692" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1692">
+        <v>6</v>
+      </c>
+      <c r="F1692" s="3">
+        <v>7.7829861111111112E-4</v>
+      </c>
+      <c r="G1692">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1693">
+        <v>2025</v>
+      </c>
+      <c r="B1693" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1693" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1693" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1693">
+        <v>7</v>
+      </c>
+      <c r="F1693" s="3">
+        <v>7.7978009259259266E-4</v>
+      </c>
+      <c r="G1693">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1694">
+        <v>2025</v>
+      </c>
+      <c r="B1694" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1694" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1694" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1694">
+        <v>8</v>
+      </c>
+      <c r="F1694" s="3">
+        <v>7.8156250000000003E-4</v>
+      </c>
+      <c r="G1694">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1695">
+        <v>2025</v>
+      </c>
+      <c r="B1695" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1695" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1695" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1695">
+        <v>9</v>
+      </c>
+      <c r="F1695" s="3">
+        <v>7.8956018518518524E-4</v>
+      </c>
+      <c r="G1695">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1696">
+        <v>2025</v>
+      </c>
+      <c r="B1696" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1696" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1696" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1696">
+        <v>10</v>
+      </c>
+      <c r="F1696" s="3">
+        <v>7.9364583333333327E-4</v>
+      </c>
+      <c r="G1696">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1697">
+        <v>2025</v>
+      </c>
+      <c r="B1697" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1697" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1697" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1697">
+        <v>1</v>
+      </c>
+      <c r="F1697">
+        <v>10.439</v>
+      </c>
+      <c r="G1697">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1698">
+        <v>2025</v>
+      </c>
+      <c r="B1698" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1698" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1698" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1698">
+        <v>2</v>
+      </c>
+      <c r="F1698">
+        <v>10.683</v>
+      </c>
+      <c r="G1698">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1699">
+        <v>2025</v>
+      </c>
+      <c r="B1699" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1699" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1699" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1699">
+        <v>3</v>
+      </c>
+      <c r="F1699">
+        <v>11.07</v>
+      </c>
+      <c r="G1699">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1700">
+        <v>2025</v>
+      </c>
+      <c r="B1700" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1700" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1700" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1700">
+        <v>4</v>
+      </c>
+      <c r="F1700">
+        <v>11.079000000000001</v>
+      </c>
+      <c r="G1700">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1701">
+        <v>2025</v>
+      </c>
+      <c r="B1701" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1701" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1701" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1701">
+        <v>5</v>
+      </c>
+      <c r="F1701">
+        <v>11.151999999999999</v>
+      </c>
+      <c r="G1701">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1702">
+        <v>2025</v>
+      </c>
+      <c r="B1702" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1702" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1702" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1702">
+        <v>6</v>
+      </c>
+      <c r="F1702">
+        <v>11.179</v>
+      </c>
+      <c r="G1702">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1703">
+        <v>2025</v>
+      </c>
+      <c r="B1703" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1703" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1703" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1703">
+        <v>7</v>
+      </c>
+      <c r="F1703">
+        <v>11.214</v>
+      </c>
+      <c r="G1703">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1704">
+        <v>2025</v>
+      </c>
+      <c r="B1704" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1704" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1704" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1704">
+        <v>8</v>
+      </c>
+      <c r="F1704">
+        <v>11.364000000000001</v>
+      </c>
+      <c r="G1704">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1705">
+        <v>2025</v>
+      </c>
+      <c r="B1705" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1705" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1705" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1705">
+        <v>9</v>
+      </c>
+      <c r="F1705">
+        <v>11.375999999999999</v>
+      </c>
+      <c r="G1705">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1706">
+        <v>2025</v>
+      </c>
+      <c r="B1706" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1706" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1706" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1706">
+        <v>10</v>
+      </c>
+      <c r="F1706">
+        <v>11.414999999999999</v>
+      </c>
+      <c r="G1706">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1707">
+        <v>2025</v>
+      </c>
+      <c r="B1707" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1707" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1707" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1707">
+        <v>1</v>
+      </c>
+      <c r="F1707" s="3">
+        <v>7.7473379629629626E-4</v>
+      </c>
+      <c r="G1707">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1708">
+        <v>2025</v>
+      </c>
+      <c r="B1708" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1708" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1708" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1708">
+        <v>2</v>
+      </c>
+      <c r="F1708" s="3">
+        <v>7.8070601851851858E-4</v>
+      </c>
+      <c r="G1708">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1709">
+        <v>2025</v>
+      </c>
+      <c r="B1709" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1709" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1709" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1709">
+        <v>3</v>
+      </c>
+      <c r="F1709" s="3">
+        <v>7.8594907407407411E-4</v>
+      </c>
+      <c r="G1709">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1710">
+        <v>2025</v>
+      </c>
+      <c r="B1710" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1710" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1710" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1710">
+        <v>4</v>
+      </c>
+      <c r="F1710" s="3">
+        <v>7.9134259259259262E-4</v>
+      </c>
+      <c r="G1710">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1711">
+        <v>2025</v>
+      </c>
+      <c r="B1711" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1711" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1711" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1711">
+        <v>5</v>
+      </c>
+      <c r="F1711" s="3">
+        <v>8.006481481481482E-4</v>
+      </c>
+      <c r="G1711">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1712">
+        <v>2025</v>
+      </c>
+      <c r="B1712" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1712" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1712" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1712">
+        <v>6</v>
+      </c>
+      <c r="F1712" s="3">
+        <v>8.214236111111112E-4</v>
+      </c>
+      <c r="G1712">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1713">
+        <v>2025</v>
+      </c>
+      <c r="B1713" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1713" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1713" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1713">
+        <v>7</v>
+      </c>
+      <c r="F1713" s="3">
+        <v>8.2925925925925919E-4</v>
+      </c>
+      <c r="G1713">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1714">
+        <v>2025</v>
+      </c>
+      <c r="B1714" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1714" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1714" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1714">
+        <v>8</v>
+      </c>
+      <c r="F1714" s="3">
+        <v>8.3471064814814812E-4</v>
+      </c>
+      <c r="G1714">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1715">
+        <v>2025</v>
+      </c>
+      <c r="B1715" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1715" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1715" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1715">
+        <v>9</v>
+      </c>
+      <c r="F1715" s="3">
+        <v>8.426736111111111E-4</v>
+      </c>
+      <c r="G1715">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1716">
+        <v>2025</v>
+      </c>
+      <c r="B1716" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1716" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1716" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1716">
+        <v>10</v>
+      </c>
+      <c r="F1716" s="3">
+        <v>8.5072916666666663E-4</v>
+      </c>
+      <c r="G1716">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1717">
+        <v>2025</v>
+      </c>
+      <c r="B1717" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1717" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1717" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1717">
+        <v>1</v>
+      </c>
+      <c r="F1717" s="3">
+        <v>3.1562152777777778E-3</v>
+      </c>
+      <c r="G1717">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1718">
+        <v>2025</v>
+      </c>
+      <c r="B1718" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1718" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1718" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1718">
+        <v>2</v>
+      </c>
+      <c r="F1718" s="3">
+        <v>3.1890046296296293E-3</v>
+      </c>
+      <c r="G1718">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1719">
+        <v>2025</v>
+      </c>
+      <c r="B1719" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1719" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1719" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1719">
+        <v>3</v>
+      </c>
+      <c r="F1719" s="3">
+        <v>3.2094675925925928E-3</v>
+      </c>
+      <c r="G1719">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1720">
+        <v>2025</v>
+      </c>
+      <c r="B1720" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1720" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1720" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1720">
+        <v>4</v>
+      </c>
+      <c r="F1720" s="3">
+        <v>3.384212962962963E-3</v>
+      </c>
+      <c r="G1720">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1721">
+        <v>2025</v>
+      </c>
+      <c r="B1721" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1721" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1721" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1721">
+        <v>5</v>
+      </c>
+      <c r="F1721" s="3">
+        <v>3.6653819444444446E-3</v>
+      </c>
+      <c r="G1721">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1722">
+        <v>2025</v>
+      </c>
+      <c r="B1722" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1722" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1722" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1722">
+        <v>6</v>
+      </c>
+      <c r="F1722" s="3">
+        <v>3.7416435185185187E-3</v>
+      </c>
+      <c r="G1722">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1723">
+        <v>2025</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1723" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1723" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1723">
+        <v>7</v>
+      </c>
+      <c r="F1723" s="3">
+        <v>3.8613310185185187E-3</v>
+      </c>
+      <c r="G1723">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1724">
+        <v>2025</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1724" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1724" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1724">
+        <v>8</v>
+      </c>
+      <c r="F1724" s="3">
+        <v>3.9044097222222223E-3</v>
+      </c>
+      <c r="G1724">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1725">
+        <v>2025</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1725" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1725" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1725">
+        <v>9</v>
+      </c>
+      <c r="F1725" s="3">
+        <v>3.9413194444444443E-3</v>
+      </c>
+      <c r="G1725">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1726">
+        <v>2025</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1726" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1726" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1726">
+        <v>1</v>
+      </c>
+      <c r="F1726">
+        <v>11.065</v>
+      </c>
+      <c r="G1726">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1727">
+        <v>2025</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1727" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1727" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1727">
+        <v>2</v>
+      </c>
+      <c r="F1727">
+        <v>11.244999999999999</v>
+      </c>
+      <c r="G1727">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1728">
+        <v>2025</v>
+      </c>
+      <c r="B1728" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1728" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1728" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1728">
+        <v>3</v>
+      </c>
+      <c r="F1728">
+        <v>11.276999999999999</v>
+      </c>
+      <c r="G1728">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1729">
+        <v>2025</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1729" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1729" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1729">
+        <v>4</v>
+      </c>
+      <c r="F1729">
+        <v>11.324999999999999</v>
+      </c>
+      <c r="G1729">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1730">
+        <v>2025</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1730" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1730" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1730">
+        <v>5</v>
+      </c>
+      <c r="F1730">
+        <v>11.513999999999999</v>
+      </c>
+      <c r="G1730">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1731">
+        <v>2025</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1731" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1731" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1731">
+        <v>6</v>
+      </c>
+      <c r="F1731">
+        <v>11.808999999999999</v>
+      </c>
+      <c r="G1731">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1732">
+        <v>2025</v>
+      </c>
+      <c r="B1732" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1732" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1732" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1732">
+        <v>7</v>
+      </c>
+      <c r="F1732">
+        <v>11.944000000000001</v>
+      </c>
+      <c r="G1732">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1733">
+        <v>2025</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1733" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1733" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1733">
+        <v>8</v>
+      </c>
+      <c r="F1733">
+        <v>12.128</v>
+      </c>
+      <c r="G1733">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1734">
+        <v>2025</v>
+      </c>
+      <c r="B1734" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1734" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1734" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1734">
+        <v>9</v>
+      </c>
+      <c r="F1734">
+        <v>12.407</v>
+      </c>
+      <c r="G1734">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1735">
+        <v>2025</v>
+      </c>
+      <c r="B1735" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1735" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1735" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1735">
+        <v>10</v>
+      </c>
+      <c r="F1735">
+        <v>12.625999999999999</v>
+      </c>
+      <c r="G1735">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1736">
+        <v>2025</v>
+      </c>
+      <c r="B1736" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1736" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1736" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1736">
+        <v>1</v>
+      </c>
+      <c r="F1736" s="3">
+        <v>9.8803240740740731E-4</v>
+      </c>
+      <c r="G1736">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1737">
+        <v>2025</v>
+      </c>
+      <c r="B1737" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1737" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1737" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1737">
+        <v>2</v>
+      </c>
+      <c r="F1737" s="3">
+        <v>1.2522453703703704E-3</v>
+      </c>
+      <c r="G1737">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1738">
+        <v>2025</v>
+      </c>
+      <c r="B1738" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1738" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1738" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1738">
+        <v>1</v>
+      </c>
+      <c r="F1738">
+        <v>14.981999999999999</v>
+      </c>
+      <c r="G1738">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1739">
+        <v>2025</v>
+      </c>
+      <c r="B1739" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1739" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1739" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1739">
+        <v>2</v>
+      </c>
+      <c r="F1739">
+        <v>18.960999999999999</v>
+      </c>
+      <c r="G1739">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1740">
+        <v>2025</v>
+      </c>
+      <c r="B1740" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1740" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1740" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1740">
+        <v>1</v>
+      </c>
+      <c r="F1740" s="3">
+        <v>9.2615740740740733E-4</v>
+      </c>
+      <c r="G1740">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1741">
+        <v>2025</v>
+      </c>
+      <c r="B1741" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1741" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1741" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1741">
+        <v>2</v>
+      </c>
+      <c r="F1741" s="3">
+        <v>9.2938657407407412E-4</v>
+      </c>
+      <c r="G1741">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1742">
+        <v>2025</v>
+      </c>
+      <c r="B1742" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1742" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1742" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1742">
+        <v>3</v>
+      </c>
+      <c r="F1742" s="3">
+        <v>9.4300925925925921E-4</v>
+      </c>
+      <c r="G1742">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1743">
+        <v>2025</v>
+      </c>
+      <c r="B1743" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1743" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1743" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1743">
+        <v>4</v>
+      </c>
+      <c r="F1743" s="3">
+        <v>1.0161111111111111E-3</v>
+      </c>
+      <c r="G1743">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1744">
+        <v>2025</v>
+      </c>
+      <c r="B1744" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1744" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1744" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1744">
+        <v>1</v>
+      </c>
+      <c r="F1744">
+        <v>13.302</v>
+      </c>
+      <c r="G1744">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1745">
+        <v>2025</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1745" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1745" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1745">
+        <v>2</v>
+      </c>
+      <c r="F1745">
+        <v>13.721</v>
+      </c>
+      <c r="G1745">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1746">
+        <v>2025</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1746" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1746" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1746">
+        <v>3</v>
+      </c>
+      <c r="F1746">
+        <v>14.135</v>
+      </c>
+      <c r="G1746">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1747">
+        <v>2025</v>
+      </c>
+      <c r="B1747" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1747" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1747" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1747">
+        <v>4</v>
+      </c>
+      <c r="F1747">
+        <v>19.04</v>
+      </c>
+      <c r="G1747">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1748">
+        <v>2025</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1748" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1748" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1748">
+        <v>1</v>
+      </c>
+      <c r="F1748" s="3">
+        <v>8.6377314814814813E-4</v>
+      </c>
+      <c r="G1748">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1749">
+        <v>2025</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1749" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1749" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1749">
+        <v>2</v>
+      </c>
+      <c r="F1749" s="3">
+        <v>8.8886574074074074E-4</v>
+      </c>
+      <c r="G1749">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1750">
+        <v>2025</v>
+      </c>
+      <c r="B1750" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1750" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1750" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1750">
+        <v>3</v>
+      </c>
+      <c r="F1750" s="3">
+        <v>9.2060185185185181E-4</v>
+      </c>
+      <c r="G1750">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1751">
+        <v>2025</v>
+      </c>
+      <c r="B1751" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1751" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1751" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1751">
+        <v>4</v>
+      </c>
+      <c r="F1751" s="3">
+        <v>9.41875E-4</v>
+      </c>
+      <c r="G1751">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1752">
+        <v>2025</v>
+      </c>
+      <c r="B1752" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1752" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1752" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1752">
+        <v>5</v>
+      </c>
+      <c r="F1752" s="3">
+        <v>9.5157407407407419E-4</v>
+      </c>
+      <c r="G1752">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1753">
+        <v>2025</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1753" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1753" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1753">
+        <v>1</v>
+      </c>
+      <c r="F1753">
+        <v>12.757</v>
+      </c>
+      <c r="G1753">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1754">
+        <v>2025</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1754" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1754" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1754">
+        <v>2</v>
+      </c>
+      <c r="F1754">
+        <v>12.766</v>
+      </c>
+      <c r="G1754">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1755">
+        <v>2025</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1755" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1755" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1755">
+        <v>3</v>
+      </c>
+      <c r="F1755">
+        <v>13.403</v>
+      </c>
+      <c r="G1755">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1756">
+        <v>2025</v>
+      </c>
+      <c r="B1756" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1756" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1756" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1756">
+        <v>4</v>
+      </c>
+      <c r="F1756">
+        <v>13.587999999999999</v>
+      </c>
+      <c r="G1756">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1757">
+        <v>2025</v>
+      </c>
+      <c r="B1757" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1757" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1757" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1757">
+        <v>5</v>
+      </c>
+      <c r="F1757">
+        <v>13.603999999999999</v>
+      </c>
+      <c r="G1757">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1758">
+        <v>2025</v>
+      </c>
+      <c r="B1758" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1758" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1758" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1758">
+        <v>6</v>
+      </c>
+      <c r="F1758">
+        <v>14.996</v>
+      </c>
+      <c r="G1758">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1759">
+        <v>2025</v>
+      </c>
+      <c r="B1759" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1759" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1759" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1759">
+        <v>1</v>
+      </c>
+      <c r="F1759" s="3">
+        <v>8.1951388888888883E-4</v>
+      </c>
+      <c r="G1759">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1760">
+        <v>2025</v>
+      </c>
+      <c r="B1760" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1760" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1760" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1760">
+        <v>2</v>
+      </c>
+      <c r="F1760" s="3">
+        <v>8.5604166666666673E-4</v>
+      </c>
+      <c r="G1760">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1761">
+        <v>2025</v>
+      </c>
+      <c r="B1761" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1761" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1761" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1761">
+        <v>3</v>
+      </c>
+      <c r="F1761" s="3">
+        <v>8.7133101851851857E-4</v>
+      </c>
+      <c r="G1761">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1762">
+        <v>2025</v>
+      </c>
+      <c r="B1762" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1762" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1762" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1762">
+        <v>4</v>
+      </c>
+      <c r="F1762" s="3">
+        <v>8.7864583333333328E-4</v>
+      </c>
+      <c r="G1762">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1763">
+        <v>2025</v>
+      </c>
+      <c r="B1763" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1763" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1763" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1763">
+        <v>5</v>
+      </c>
+      <c r="F1763" s="3">
+        <v>9.093402777777779E-4</v>
+      </c>
+      <c r="G1763">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1764">
+        <v>2025</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1764" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1764" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1764">
+        <v>6</v>
+      </c>
+      <c r="F1764" s="3">
+        <v>1.051388888888889E-3</v>
+      </c>
+      <c r="G1764">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1765">
+        <v>2025</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1765" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1765" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1765">
+        <v>1</v>
+      </c>
+      <c r="F1765">
+        <v>12.178000000000001</v>
+      </c>
+      <c r="G1765">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1766">
+        <v>2025</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1766" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1766" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1766">
+        <v>2</v>
+      </c>
+      <c r="F1766">
+        <v>12.217000000000001</v>
+      </c>
+      <c r="G1766">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1767">
+        <v>2025</v>
+      </c>
+      <c r="B1767" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1767" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1767" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1767">
+        <v>3</v>
+      </c>
+      <c r="F1767">
+        <v>12.33</v>
+      </c>
+      <c r="G1767">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1768">
+        <v>2025</v>
+      </c>
+      <c r="B1768" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1768" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1768" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1768">
+        <v>4</v>
+      </c>
+      <c r="F1768">
+        <v>13.05</v>
+      </c>
+      <c r="G1768">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1769">
+        <v>2025</v>
+      </c>
+      <c r="B1769" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1769" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1769" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1769">
+        <v>5</v>
+      </c>
+      <c r="F1769">
+        <v>15.074</v>
+      </c>
+      <c r="G1769">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1770">
+        <v>2025</v>
+      </c>
+      <c r="B1770" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1770" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1770" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1770">
+        <v>1</v>
+      </c>
+      <c r="F1770" s="3">
+        <v>8.3709490740740749E-4</v>
+      </c>
+      <c r="G1770">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1771">
+        <v>2025</v>
+      </c>
+      <c r="B1771" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1771" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1771" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1771">
+        <v>2</v>
+      </c>
+      <c r="F1771" s="3">
+        <v>8.4773148148148143E-4</v>
+      </c>
+      <c r="G1771">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1772">
+        <v>2025</v>
+      </c>
+      <c r="B1772" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1772" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1772" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1772">
+        <v>3</v>
+      </c>
+      <c r="F1772" s="3">
+        <v>8.7082175925925934E-4</v>
+      </c>
+      <c r="G1772">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1773">
+        <v>2025</v>
+      </c>
+      <c r="B1773" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1773" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1773" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1773">
+        <v>4</v>
+      </c>
+      <c r="F1773" s="3">
+        <v>8.7464120370370376E-4</v>
+      </c>
+      <c r="G1773">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1774">
+        <v>2025</v>
+      </c>
+      <c r="B1774" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1774" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1774" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1774">
+        <v>5</v>
+      </c>
+      <c r="F1774" s="3">
+        <v>8.7846064814814818E-4</v>
+      </c>
+      <c r="G1774">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1775">
+        <v>2025</v>
+      </c>
+      <c r="B1775" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1775" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1775" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1775">
+        <v>6</v>
+      </c>
+      <c r="F1775" s="3">
+        <v>8.8828703703703704E-4</v>
+      </c>
+      <c r="G1775">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1776">
+        <v>2025</v>
+      </c>
+      <c r="B1776" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1776" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1776" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1776">
+        <v>7</v>
+      </c>
+      <c r="F1776" s="3">
+        <v>9.0489583333333329E-4</v>
+      </c>
+      <c r="G1776">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1777">
+        <v>2025</v>
+      </c>
+      <c r="B1777" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1777" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1777" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1777">
+        <v>8</v>
+      </c>
+      <c r="F1777" s="3">
+        <v>9.2543981481481481E-4</v>
+      </c>
+      <c r="G1777">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1778">
+        <v>2025</v>
+      </c>
+      <c r="B1778" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1778" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1778" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1778">
+        <v>9</v>
+      </c>
+      <c r="F1778" s="3">
+        <v>9.5795138888888883E-4</v>
+      </c>
+      <c r="G1778">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1779">
+        <v>2025</v>
+      </c>
+      <c r="B1779" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1779" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1779" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1779">
+        <v>10</v>
+      </c>
+      <c r="F1779" s="3">
+        <v>9.6258101851851854E-4</v>
+      </c>
+      <c r="G1779">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1780">
+        <v>2025</v>
+      </c>
+      <c r="B1780" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1780" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1780" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1780">
+        <v>1</v>
+      </c>
+      <c r="F1780">
+        <v>11.686</v>
+      </c>
+      <c r="G1780">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1781">
+        <v>2025</v>
+      </c>
+      <c r="B1781" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1781" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1781" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1781">
+        <v>2</v>
+      </c>
+      <c r="F1781">
+        <v>12.125</v>
+      </c>
+      <c r="G1781">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1782">
+        <v>2025</v>
+      </c>
+      <c r="B1782" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1782" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1782" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1782">
+        <v>3</v>
+      </c>
+      <c r="F1782">
+        <v>12.561999999999999</v>
+      </c>
+      <c r="G1782">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1783">
+        <v>2025</v>
+      </c>
+      <c r="B1783" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1783" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1783" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1783">
+        <v>4</v>
+      </c>
+      <c r="F1783">
+        <v>12.64</v>
+      </c>
+      <c r="G1783">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1784">
+        <v>2025</v>
+      </c>
+      <c r="B1784" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1784" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1784" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1784">
+        <v>5</v>
+      </c>
+      <c r="F1784">
+        <v>12.801</v>
+      </c>
+      <c r="G1784">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1785">
+        <v>2025</v>
+      </c>
+      <c r="B1785" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1785" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1785" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1785">
+        <v>6</v>
+      </c>
+      <c r="F1785">
+        <v>13.25</v>
+      </c>
+      <c r="G1785">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A1786">
+        <v>2025</v>
+      </c>
+      <c r="B1786" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1786" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1786" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1786">
+        <v>7</v>
+      </c>
+      <c r="F1786">
+        <v>14.512</v>
+      </c>
+      <c r="G1786">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1788">
+        <f>SUBTOTAL(5,A2:A1786)</f>
+        <v>2025</v>
+      </c>
+      <c r="F1788" s="4">
+        <f>SUBTOTAL(1,F2:F1786)</f>
+        <v>1.1201388888888888E-3</v>
+      </c>
+      <c r="G1788">
+        <f>SUBTOTAL(1,G2:G1786)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1789">
+        <f>SUBTOTAL(4,A2:A1786)</f>
+        <v>2025</v>
+      </c>
+      <c r="F1789" s="5">
+        <f>SUBTOTAL(1,F2:F1786)</f>
+        <v>1.1201388888888888E-3</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:F1267 A1268:E1277 A1278:D1297 A1298:A1480 A1582:B1591">
-    <cfRule type="expression" dxfId="14" priority="55">
+  <conditionalFormatting sqref="A2:F1267 A1268:E1277 A1278:D1297 A1298:A1480 D1328:D1786">
+    <cfRule type="expression" dxfId="14" priority="58">
       <formula>$E2&lt;4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="56">
+    <cfRule type="expression" dxfId="13" priority="59">
       <formula>$E2&gt;6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="57">
+    <cfRule type="expression" dxfId="12" priority="60">
       <formula>$E2&gt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1328:C1480">
-    <cfRule type="expression" dxfId="11" priority="31">
+    <cfRule type="expression" dxfId="11" priority="34">
       <formula>$E1328&lt;4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="32">
+    <cfRule type="expression" dxfId="10" priority="35">
       <formula>$E1328&gt;6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="33">
+    <cfRule type="expression" dxfId="9" priority="36">
       <formula>$E1328&gt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1298:D1327">
-    <cfRule type="expression" dxfId="8" priority="46">
+    <cfRule type="expression" dxfId="8" priority="49">
       <formula>$E1298&lt;4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="47">
+    <cfRule type="expression" dxfId="7" priority="50">
       <formula>$E1298&gt;6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="48">
+    <cfRule type="expression" dxfId="6" priority="51">
       <formula>$E1298&gt;3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1328:D1581">
-    <cfRule type="expression" dxfId="5" priority="37">
-      <formula>$E1328&lt;4</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="38">
-      <formula>$E1328&gt;6</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="39">
-      <formula>$E1328&gt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E1278:E1591 A1481:C1581">
-    <cfRule type="expression" dxfId="2" priority="1">
+  <conditionalFormatting sqref="A1481:C1786 E1278:E1786">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>$E1278&lt;4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>$E1278&gt;6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="3" priority="6">
       <formula>$E1278&gt;3</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F1789">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>$E1789&lt;4</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$E1789&gt;6</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>$E1789&gt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{3A4CF648-6AED-40f4-86FF-DC5316D8AED3}">
       <x14:slicerList xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
-        <x14:slicer r:id="rId3"/>
+        <x14:slicer r:id="rId4"/>
       </x14:slicerList>
     </ext>
   </extLst>

--- a/pages/ParaFactorTool/Para_4year_data_track.xlsx
+++ b/pages/ParaFactorTool/Para_4year_data_track.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\ParaFactorTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D036FB7-1679-46A5-BC64-7CC17D4B3CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2253DED-B268-40B5-B8B1-CD9CDBBE769A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{398C2CAE-8513-48E9-A3F5-2A4019774188}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{398C2CAE-8513-48E9-A3F5-2A4019774188}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="WB IP prediction" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$1786</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'WB IP prediction'!$A$11:$G$23</definedName>
     <definedName name="Slicer_Class">#N/A</definedName>
     <definedName name="Slicer_Event">#N/A</definedName>
     <definedName name="Slicer_Rank">#N/A</definedName>
@@ -29,10 +31,10 @@
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{46BE6895-7355-4a93-B00E-2C351335B9C9}">
       <x15:slicerCaches xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
-        <x14:slicerCache r:id="rId2"/>
         <x14:slicerCache r:id="rId3"/>
         <x14:slicerCache r:id="rId4"/>
         <x14:slicerCache r:id="rId5"/>
+        <x14:slicerCache r:id="rId6"/>
       </x15:slicerCaches>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -53,8 +55,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5362" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5620" uniqueCount="54">
   <si>
     <t>Year</t>
   </si>
@@ -112,17 +136,125 @@
   <si>
     <t>Participants</t>
   </si>
+  <si>
+    <t>WCH</t>
+  </si>
+  <si>
+    <t>1st</t>
+  </si>
+  <si>
+    <t>2nd</t>
+  </si>
+  <si>
+    <t>3rd</t>
+  </si>
+  <si>
+    <t>4th</t>
+  </si>
+  <si>
+    <t>5th</t>
+  </si>
+  <si>
+    <t>6th</t>
+  </si>
+  <si>
+    <t>7th</t>
+  </si>
+  <si>
+    <t>8th</t>
+  </si>
+  <si>
+    <t>9th</t>
+  </si>
+  <si>
+    <t>Scale 1</t>
+  </si>
+  <si>
+    <t>Scale 2</t>
+  </si>
+  <si>
+    <t>Scale 3</t>
+  </si>
+  <si>
+    <t>Scale 4</t>
+  </si>
+  <si>
+    <t>Scale 5</t>
+  </si>
+  <si>
+    <t>Scale 6</t>
+  </si>
+  <si>
+    <t>Scale 7</t>
+  </si>
+  <si>
+    <t>Scale 8</t>
+  </si>
+  <si>
+    <t>Scale 9</t>
+  </si>
+  <si>
+    <t>OLY</t>
+  </si>
+  <si>
+    <t>2028 3k</t>
+  </si>
+  <si>
+    <t>5% drop off in 2025</t>
+  </si>
+  <si>
+    <t>slow down using drop off</t>
+  </si>
+  <si>
+    <t>Seconds</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Conversion factor</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t>Improvement</t>
+  </si>
+  <si>
+    <t>Paralympic time</t>
+  </si>
+  <si>
+    <t>World Champs time</t>
+  </si>
+  <si>
+    <t>2025 WCH</t>
+  </si>
+  <si>
+    <t>2025 PLY</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="mm:ss.000"/>
-    <numFmt numFmtId="173" formatCode="0.000"/>
-    <numFmt numFmtId="174" formatCode="m:ss.000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="m:ss.000"/>
+    <numFmt numFmtId="173" formatCode="0.0"/>
+    <numFmt numFmtId="174" formatCode="mm:ss.00"/>
+    <numFmt numFmtId="175" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,8 +268,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FF242E35"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -150,8 +303,32 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -170,22 +347,192 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="174" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="47" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="47" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="47" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="31">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -307,19 +654,3990 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'WB IP prediction'!$A$1:$A$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'WB IP prediction'!$D$1:$D$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>205.78876164707225</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200.81899999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>203.65600000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>201.75900000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>205.37199999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D6F0-4256-AB3F-B0C186CDB0B2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1426181312"/>
+        <c:axId val="1426183232"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1426181312"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1426183232"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1426183232"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1426181312"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-NZ" sz="1600"/>
+              <a:t>Paralympic</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-NZ" sz="1600" baseline="0"/>
+              <a:t> WB 3000m IP top qualifying time by year</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-NZ" sz="1600"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-4.9444236756377886E-2"/>
+                  <c:y val="-0.1930366598739009"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'WB IP prediction'!$I$55:$I$59</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'WB IP prediction'!$J$55:$J$59</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>218.08500000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>211.52999999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>207.46</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>199.483</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>197.64299999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-902D-4E2D-A0B9-EE19F1548A20}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>4000</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="2.8369633087014172E-2"/>
+                  <c:y val="-0.12376640459312652"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'WB IP prediction'!$I$55:$I$59</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'WB IP prediction'!$K$55:$K$59</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>290.05305000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>281.3349</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>275.92180000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>265.31238999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>262.86518999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-902D-4E2D-A0B9-EE19F1548A20}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1248224432"/>
+        <c:axId val="1248209072"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1248224432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-NZ" sz="1400"/>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1248209072"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1248209072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="180"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-NZ" sz="1400"/>
+                  <a:t>Seconds</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1248224432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.1391076115485565E-3"/>
+                  <c:y val="-0.42924136864017404"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'WB IP prediction'!$I$69:$I$75</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'WB IP prediction'!$J$69:$J$75</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>211.69300000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>212.15100000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>205.78876164707225</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>200.81899999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>203.65600000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>201.75900000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>205.37199999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4056-40D0-A4A5-5C9F81B9F13E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1208928656"/>
+        <c:axId val="1208929616"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1208928656"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1208929616"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1208929616"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1208928656"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-4.4449912510936135E-2"/>
+                  <c:y val="-0.50028871391076113"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'WB IP prediction'!$A$81:$A$86</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2028</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'WB IP prediction'!$B$81:$B$86</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>290.05305000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>281.3349</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>275.92180000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>265.31238999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>262.86518999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>254.6670303192931</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8845-4A78-9653-35CC7731A978}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1583153120"/>
+        <c:axId val="1583148800"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1583153120"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1583148800"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1583148800"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1583153120"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>152766</xdr:colOff>
-      <xdr:row>1736</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>628650</xdr:colOff>
-      <xdr:row>1798</xdr:row>
+      <xdr:row>339</xdr:row>
       <xdr:rowOff>144336</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -391,13 +4709,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>86821</xdr:colOff>
-      <xdr:row>1736</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>74734</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>630847</xdr:colOff>
-      <xdr:row>1799</xdr:row>
+      <xdr:row>340</xdr:row>
       <xdr:rowOff>29671</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -469,13 +4787,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>169615</xdr:colOff>
-      <xdr:row>1799</xdr:row>
+      <xdr:row>340</xdr:row>
       <xdr:rowOff>38097</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>730</xdr:colOff>
-      <xdr:row>1812</xdr:row>
+      <xdr:row>763</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -547,13 +4865,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>106237</xdr:colOff>
-      <xdr:row>1799</xdr:row>
+      <xdr:row>340</xdr:row>
       <xdr:rowOff>87188</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>732</xdr:colOff>
-      <xdr:row>1816</xdr:row>
+      <xdr:row>1147</xdr:row>
       <xdr:rowOff>38829</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -624,6 +4942,155 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>54768</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>92868</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D2C3ED7-F267-C80D-63CD-22A23F7C754E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>248730</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>51946</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>161684</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>137672</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F29056D8-E027-8F4B-4000-3D6249D87356}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>642937</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>179614</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>44223</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>167368</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{323C6CF4-A999-530B-85A3-7EAF07396844}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>299757</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>87966</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>322168</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>141754</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CEE189F-0769-1A9C-B5B2-17186AD52F7F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Event" xr10:uid="{1CAF9550-9637-4FBE-AA97-0EFAA12C83D7}" sourceName="Event">
   <extLst>
@@ -669,43 +5136,26 @@
   <slicer name="Event" xr10:uid="{41021184-9E7A-4968-B432-0FF46B91C25D}" cache="Slicer_Event" caption="Event" rowHeight="241300"/>
   <slicer name="Class" xr10:uid="{14C2EB51-BA5F-4AC2-A8A8-0F93C0B4B6CD}" cache="Slicer_Class" caption="Class" rowHeight="241300"/>
   <slicer name="Sex" xr10:uid="{B817BF0C-F847-4C6B-A034-BC5238F3261D}" cache="Slicer_Sex" caption="Sex" rowHeight="241300"/>
-  <slicer name="Rank" xr10:uid="{C470A3FB-E70B-4D95-8A29-5D81A9EC43CD}" cache="Slicer_Rank" caption="Rank" rowHeight="241300"/>
+  <slicer name="Rank" xr10:uid="{C470A3FB-E70B-4D95-8A29-5D81A9EC43CD}" cache="Slicer_Rank" caption="Rank" startItem="1" rowHeight="241300"/>
 </slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BD10C5AC-6F69-4783-B825-21587748049F}" name="Table2" displayName="Table2" ref="A1:G1786" totalsRowShown="0">
   <autoFilter ref="A1:G1786" xr:uid="{963A9C9A-A891-4AE2-AB26-5E2EF12B3783}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="2022"/>
-        <filter val="2023"/>
-        <filter val="2024"/>
-        <filter val="2025"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="Kilo"/>
+        <filter val="IP"/>
       </filters>
     </filterColumn>
     <filterColumn colId="2">
       <filters>
-        <filter val="C1"/>
+        <filter val="B"/>
       </filters>
     </filterColumn>
     <filterColumn colId="3">
       <filters>
         <filter val="F"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="4">
-      <filters>
-        <filter val="1"/>
-        <filter val="2"/>
-        <filter val="3"/>
-        <filter val="4"/>
-        <filter val="5"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -715,7 +5165,7 @@
     <tableColumn id="3" xr3:uid="{6A0738BF-EB18-4C14-8369-03EA5927D197}" name="Class"/>
     <tableColumn id="4" xr3:uid="{9B34D095-156E-436C-95D8-A66C22E64416}" name="Sex"/>
     <tableColumn id="5" xr3:uid="{913130A9-EA80-4376-B771-805DC532B8F1}" name="Rank"/>
-    <tableColumn id="6" xr3:uid="{6833436A-6E62-49C6-9833-A7CFB575AA67}" name="Time" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{6833436A-6E62-49C6-9833-A7CFB575AA67}" name="Time" dataDxfId="30"/>
     <tableColumn id="7" xr3:uid="{D30E61A1-A654-4C07-B50C-C93493F03A58}" name="Participants"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1515,7 +5965,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>2019</v>
       </c>
@@ -1538,7 +5988,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>2019</v>
       </c>
@@ -1561,7 +6011,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>2019</v>
       </c>
@@ -1584,7 +6034,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>2019</v>
       </c>
@@ -1607,7 +6057,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>2019</v>
       </c>
@@ -1630,7 +6080,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>2019</v>
       </c>
@@ -1653,7 +6103,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>2019</v>
       </c>
@@ -1676,7 +6126,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>2019</v>
       </c>
@@ -1699,7 +6149,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>2019</v>
       </c>
@@ -1722,7 +6172,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>2019</v>
       </c>
@@ -8737,7 +13187,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A336">
         <v>2020</v>
       </c>
@@ -8760,7 +13210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A337">
         <v>2020</v>
       </c>
@@ -8783,7 +13233,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A338">
         <v>2020</v>
       </c>
@@ -8806,7 +13256,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A339">
         <v>2020</v>
       </c>
@@ -8829,7 +13279,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A340">
         <v>2020</v>
       </c>
@@ -8852,7 +13302,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A341">
         <v>2020</v>
       </c>
@@ -8875,7 +13325,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A342">
         <v>2020</v>
       </c>
@@ -8898,7 +13348,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A343">
         <v>2020</v>
       </c>
@@ -8921,7 +13371,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="344" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A344">
         <v>2020</v>
       </c>
@@ -8944,7 +13394,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A345">
         <v>2020</v>
       </c>
@@ -18406,7 +22856,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="756" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="756" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A756">
         <v>2022</v>
       </c>
@@ -18429,7 +22879,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="757" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="757" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A757">
         <v>2022</v>
       </c>
@@ -18452,7 +22902,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="758" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="758" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A758">
         <v>2022</v>
       </c>
@@ -18475,7 +22925,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="759" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="759" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A759">
         <v>2022</v>
       </c>
@@ -18498,7 +22948,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="760" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="760" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A760">
         <v>2022</v>
       </c>
@@ -18521,7 +22971,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="761" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="761" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A761">
         <v>2022</v>
       </c>
@@ -18544,7 +22994,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="762" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="762" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A762">
         <v>2022</v>
       </c>
@@ -18567,7 +23017,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="763" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="763" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A763">
         <v>2022</v>
       </c>
@@ -18590,7 +23040,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="764" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="764" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A764">
         <v>2022</v>
       </c>
@@ -18613,7 +23063,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="765" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="765" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A765">
         <v>2022</v>
       </c>
@@ -27376,7 +31826,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1146" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1146" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1146">
         <v>2023</v>
       </c>
@@ -27399,7 +31849,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1147" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1147" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1147">
         <v>2023</v>
       </c>
@@ -27422,7 +31872,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1148" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1148" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1148">
         <v>2023</v>
       </c>
@@ -27445,7 +31895,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1149" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1149" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1149">
         <v>2023</v>
       </c>
@@ -27468,7 +31918,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1150" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1150" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1150">
         <v>2023</v>
       </c>
@@ -27491,7 +31941,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1151" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1151" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1151">
         <v>2023</v>
       </c>
@@ -27514,7 +31964,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1152" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1152" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1152">
         <v>2023</v>
       </c>
@@ -27537,7 +31987,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1153" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1153" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1153">
         <v>2023</v>
       </c>
@@ -27560,7 +32010,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1154" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1154" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1154">
         <v>2023</v>
       </c>
@@ -27583,7 +32033,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1155" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1155" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1155">
         <v>2023</v>
       </c>
@@ -34322,7 +38772,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1448" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1448" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1448">
         <v>2024</v>
       </c>
@@ -34345,7 +38795,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1449" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1449" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1449">
         <v>2024</v>
       </c>
@@ -34368,7 +38818,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1450" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1450" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1450">
         <v>2024</v>
       </c>
@@ -34391,7 +38841,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1451" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1451" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1451">
         <v>2024</v>
       </c>
@@ -34414,7 +38864,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1452" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1452" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1452">
         <v>2024</v>
       </c>
@@ -34437,7 +38887,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1453" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1453" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1453">
         <v>2024</v>
       </c>
@@ -34460,7 +38910,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1454" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1454" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1454">
         <v>2024</v>
       </c>
@@ -34483,7 +38933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1455" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1455" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1455">
         <v>2024</v>
       </c>
@@ -34506,7 +38956,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1456" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1456" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1456">
         <v>2024</v>
       </c>
@@ -34529,7 +38979,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1457" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1457" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1457">
         <v>2024</v>
       </c>
@@ -40529,7 +44979,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1717" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1717" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1717">
         <v>2025</v>
       </c>
@@ -40552,7 +45002,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1718" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1718" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1718">
         <v>2025</v>
       </c>
@@ -40575,7 +45025,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1719" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1719" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1719">
         <v>2025</v>
       </c>
@@ -40598,7 +45048,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1720" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1720" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1720">
         <v>2025</v>
       </c>
@@ -40621,7 +45071,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1721" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1721" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1721">
         <v>2025</v>
       </c>
@@ -40644,7 +45094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1722" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1722" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1722">
         <v>2025</v>
       </c>
@@ -40667,7 +45117,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1723" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1723" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1723">
         <v>2025</v>
       </c>
@@ -40690,7 +45140,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1724" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1724" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1724">
         <v>2025</v>
       </c>
@@ -40713,7 +45163,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1725" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1725" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1725">
         <v>2025</v>
       </c>
@@ -40966,7 +45416,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1736" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1736" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1736">
         <v>2025</v>
       </c>
@@ -40989,7 +45439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1737" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1737" spans="1:7" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1737">
         <v>2025</v>
       </c>
@@ -42142,15 +46592,15 @@
     <row r="1788" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1788">
         <f>SUBTOTAL(5,A2:A1786)</f>
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="F1788" s="4">
         <f>SUBTOTAL(1,F2:F1786)</f>
-        <v>1.1201388888888888E-3</v>
+        <v>2.6758230616259573E-3</v>
       </c>
       <c r="G1788">
         <f>SUBTOTAL(1,G2:G1786)</f>
-        <v>2</v>
+        <v>12.728813559322035</v>
       </c>
     </row>
     <row r="1789" spans="1:7" x14ac:dyDescent="0.45">
@@ -42160,63 +46610,63 @@
       </c>
       <c r="F1789" s="5">
         <f>SUBTOTAL(1,F2:F1786)</f>
-        <v>1.1201388888888888E-3</v>
+        <v>2.6758230616259573E-3</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:F1267 A1268:E1277 A1278:D1297 A1298:A1480 D1328:D1786">
-    <cfRule type="expression" dxfId="14" priority="58">
+    <cfRule type="expression" dxfId="29" priority="58">
       <formula>$E2&lt;4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="59">
+    <cfRule type="expression" dxfId="28" priority="59">
       <formula>$E2&gt;6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="60">
+    <cfRule type="expression" dxfId="27" priority="60">
       <formula>$E2&gt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1328:C1480">
-    <cfRule type="expression" dxfId="11" priority="34">
+    <cfRule type="expression" dxfId="26" priority="34">
       <formula>$E1328&lt;4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="35">
+    <cfRule type="expression" dxfId="25" priority="35">
       <formula>$E1328&gt;6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="36">
+    <cfRule type="expression" dxfId="24" priority="36">
       <formula>$E1328&gt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1298:D1327">
-    <cfRule type="expression" dxfId="8" priority="49">
+    <cfRule type="expression" dxfId="23" priority="49">
       <formula>$E1298&lt;4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="50">
+    <cfRule type="expression" dxfId="22" priority="50">
       <formula>$E1298&gt;6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="51">
+    <cfRule type="expression" dxfId="21" priority="51">
       <formula>$E1298&gt;3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1481:C1786 E1278:E1786">
-    <cfRule type="expression" dxfId="5" priority="4">
+  <conditionalFormatting sqref="E1278:E1786 A1481:C1786">
+    <cfRule type="expression" dxfId="20" priority="4">
       <formula>$E1278&lt;4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="19" priority="5">
       <formula>$E1278&gt;6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="6">
+    <cfRule type="expression" dxfId="18" priority="6">
       <formula>$E1278&gt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1789">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>$E1789&lt;4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="16" priority="2">
       <formula>$E1789&gt;6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="15" priority="3">
       <formula>$E1789&gt;3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42234,4 +46684,3493 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECED1680-AA5F-4E5A-A3DB-8DB035FF2C31}">
+  <dimension ref="A1:XFD127"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="11" max="11" width="13.86328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="7">
+        <v>2019</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1">
+        <v>2.3818143709151882E-3</v>
+      </c>
+      <c r="D1">
+        <f>C1*86400</f>
+        <v>205.78876164707225</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="9">
+        <v>2020</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2">
+        <v>2.3242939814814814E-3</v>
+      </c>
+      <c r="D2">
+        <f t="shared" ref="D2:D6" si="0">C2*86400</f>
+        <v>200.81899999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" s="7">
+        <v>2022</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3">
+        <v>2.3571296296296296E-3</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="0"/>
+        <v>203.65600000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="9">
+        <v>2023</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4">
+        <v>2.3351736111111112E-3</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>201.75900000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5">
+        <v>2.3769907407407407E-3</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>205.37199999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6">
+        <v>3.1562152777777778E-3</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>272.697</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A12" s="7">
+        <v>2019</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11">
+        <v>2.3818143709151882E-3</v>
+      </c>
+      <c r="G12">
+        <f>F12*86400</f>
+        <v>205.78876164707225</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" s="7">
+        <v>2020</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1</v>
+      </c>
+      <c r="F13" s="11">
+        <v>2.3242939814814814E-3</v>
+      </c>
+      <c r="G13">
+        <f>F13*86400</f>
+        <v>200.81899999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A14" s="7">
+        <v>2022</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1</v>
+      </c>
+      <c r="F14" s="11">
+        <v>2.3571296296296296E-3</v>
+      </c>
+      <c r="G14">
+        <f>F14*86400</f>
+        <v>203.65600000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A15" s="7">
+        <v>2023</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1</v>
+      </c>
+      <c r="F15" s="11">
+        <v>2.3351736111111112E-3</v>
+      </c>
+      <c r="G15">
+        <f>F15*86400</f>
+        <v>201.75900000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A16" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1</v>
+      </c>
+      <c r="F16" s="13">
+        <v>2.3769907407407407E-3</v>
+      </c>
+      <c r="G16">
+        <f>F16*86400</f>
+        <v>205.37199999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A17" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1</v>
+      </c>
+      <c r="F17" s="13">
+        <v>3.1562152777777778E-3</v>
+      </c>
+      <c r="G17">
+        <f>F17*86400</f>
+        <v>272.697</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A18" s="9">
+        <v>2019</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="6">
+        <v>2</v>
+      </c>
+      <c r="F18" s="12">
+        <v>2.4294015898003998E-3</v>
+      </c>
+      <c r="G18">
+        <f>F18*86400</f>
+        <v>209.90029735875453</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A19" s="9">
+        <v>2020</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="6">
+        <v>2</v>
+      </c>
+      <c r="F19" s="12">
+        <v>2.3999768518518519E-3</v>
+      </c>
+      <c r="G19">
+        <f>F19*86400</f>
+        <v>207.358</v>
+      </c>
+      <c r="K19" t="s">
+        <v>20</v>
+      </c>
+      <c r="L19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" t="s">
+        <v>22</v>
+      </c>
+      <c r="N19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O19" t="s">
+        <v>24</v>
+      </c>
+      <c r="P19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>26</v>
+      </c>
+      <c r="R19" t="s">
+        <v>27</v>
+      </c>
+      <c r="S19" t="s">
+        <v>28</v>
+      </c>
+      <c r="U19" t="s">
+        <v>29</v>
+      </c>
+      <c r="V19" t="s">
+        <v>30</v>
+      </c>
+      <c r="W19" t="s">
+        <v>31</v>
+      </c>
+      <c r="X19" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A20" s="9">
+        <v>2022</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="6">
+        <v>2</v>
+      </c>
+      <c r="F20" s="12">
+        <v>2.442800925925926E-3</v>
+      </c>
+      <c r="G20">
+        <f>F20*86400</f>
+        <v>211.05799999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A21" s="9">
+        <v>2023</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="6">
+        <v>2</v>
+      </c>
+      <c r="F21" s="12">
+        <v>2.3375347222222222E-3</v>
+      </c>
+      <c r="G21">
+        <f>F21*86400</f>
+        <v>201.96299999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A22" s="9">
+        <v>2024</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="6">
+        <v>2</v>
+      </c>
+      <c r="F22" s="14">
+        <v>2.3835648148148149E-3</v>
+      </c>
+      <c r="G22">
+        <f>F22*86400</f>
+        <v>205.94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A23" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="6">
+        <v>2</v>
+      </c>
+      <c r="F23" s="14">
+        <v>3.1890046296296293E-3</v>
+      </c>
+      <c r="G23">
+        <f>F23*86400</f>
+        <v>275.52999999999997</v>
+      </c>
+      <c r="I23">
+        <v>2008</v>
+      </c>
+      <c r="J23" t="s">
+        <v>38</v>
+      </c>
+      <c r="K23" s="15">
+        <v>218.08500000000004</v>
+      </c>
+      <c r="L23" s="15">
+        <v>220.99700000000004</v>
+      </c>
+      <c r="M23" s="15">
+        <v>222.23699999999999</v>
+      </c>
+      <c r="N23" s="15">
+        <v>227.27100000000002</v>
+      </c>
+      <c r="O23" s="15">
+        <v>230.51499999999999</v>
+      </c>
+      <c r="P23" s="15">
+        <v>234.32200000000003</v>
+      </c>
+      <c r="Q23" s="15">
+        <v>234.90899999999999</v>
+      </c>
+      <c r="R23" s="15">
+        <v>239.328</v>
+      </c>
+      <c r="S23" s="15">
+        <v>242.82000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A24" s="7">
+        <v>2019</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="8">
+        <v>3</v>
+      </c>
+      <c r="F24" s="11">
+        <v>2.4367896758095016E-3</v>
+      </c>
+      <c r="G24">
+        <f>F24*86400</f>
+        <v>210.53862798994095</v>
+      </c>
+      <c r="I24">
+        <v>2008</v>
+      </c>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="16"/>
+      <c r="S24" s="16"/>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A25" s="7">
+        <v>2020</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" s="8">
+        <v>3</v>
+      </c>
+      <c r="F25" s="11">
+        <v>2.4202314814814811E-3</v>
+      </c>
+      <c r="G25">
+        <f>F25*86400</f>
+        <v>209.10799999999998</v>
+      </c>
+      <c r="I25">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A26" s="7">
+        <v>2022</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="8">
+        <v>3</v>
+      </c>
+      <c r="F26" s="11">
+        <v>2.5088773148148149E-3</v>
+      </c>
+      <c r="G26">
+        <f>F26*86400</f>
+        <v>216.767</v>
+      </c>
+      <c r="I26">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A27" s="7">
+        <v>2023</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="8">
+        <v>3</v>
+      </c>
+      <c r="F27" s="11">
+        <v>2.388912037037037E-3</v>
+      </c>
+      <c r="G27">
+        <f>F27*86400</f>
+        <v>206.40199999999999</v>
+      </c>
+      <c r="I27">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A28" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="8">
+        <v>3</v>
+      </c>
+      <c r="F28" s="13">
+        <v>2.4154976851851855E-3</v>
+      </c>
+      <c r="G28">
+        <f>F28*86400</f>
+        <v>208.69900000000001</v>
+      </c>
+      <c r="I28">
+        <v>2012</v>
+      </c>
+      <c r="J28" t="s">
+        <v>38</v>
+      </c>
+      <c r="K28" s="15">
+        <v>211.52999999999997</v>
+      </c>
+      <c r="L28" s="15">
+        <v>216.453</v>
+      </c>
+      <c r="M28" s="15">
+        <v>216.92999999999998</v>
+      </c>
+      <c r="N28" s="15">
+        <v>223.33500000000001</v>
+      </c>
+      <c r="O28" s="15">
+        <v>225.69799999999998</v>
+      </c>
+      <c r="P28" s="15">
+        <v>226.697</v>
+      </c>
+      <c r="Q28" s="15">
+        <v>231.10300000000004</v>
+      </c>
+      <c r="R28" s="15">
+        <v>241.417</v>
+      </c>
+      <c r="S28" s="15">
+        <v>241.44900000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A29" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" s="8">
+        <v>3</v>
+      </c>
+      <c r="F29" s="13">
+        <v>3.2094675925925928E-3</v>
+      </c>
+      <c r="G29">
+        <f>F29*86400</f>
+        <v>277.298</v>
+      </c>
+      <c r="I29">
+        <v>2012</v>
+      </c>
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
+      <c r="M29" s="16"/>
+      <c r="N29" s="16"/>
+      <c r="O29" s="16"/>
+      <c r="P29" s="16"/>
+      <c r="Q29" s="16"/>
+      <c r="R29" s="16"/>
+      <c r="S29" s="16"/>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A30" s="9">
+        <v>2019</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E30" s="6">
+        <v>4</v>
+      </c>
+      <c r="F30" s="12">
+        <v>2.440834179489182E-3</v>
+      </c>
+      <c r="G30">
+        <f>F30*86400</f>
+        <v>210.88807310786532</v>
+      </c>
+      <c r="I30">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A31" s="9">
+        <v>2020</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E31" s="6">
+        <v>4</v>
+      </c>
+      <c r="F31" s="12">
+        <v>2.437789351851852E-3</v>
+      </c>
+      <c r="G31">
+        <f>F31*86400</f>
+        <v>210.625</v>
+      </c>
+      <c r="I31">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A32" s="9">
+        <v>2022</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="6">
+        <v>4</v>
+      </c>
+      <c r="F32" s="12">
+        <v>2.5763773148148148E-3</v>
+      </c>
+      <c r="G32">
+        <f>F32*86400</f>
+        <v>222.59899999999999</v>
+      </c>
+      <c r="I32">
+        <v>2016</v>
+      </c>
+      <c r="J32" t="s">
+        <v>19</v>
+      </c>
+      <c r="K32" s="15">
+        <v>211.69300000000001</v>
+      </c>
+      <c r="L32" s="15">
+        <v>215.47900000000001</v>
+      </c>
+      <c r="M32" s="15">
+        <v>215.78399999999996</v>
+      </c>
+      <c r="N32" s="15">
+        <v>215.92400000000001</v>
+      </c>
+      <c r="O32" s="15">
+        <v>222.07999999999996</v>
+      </c>
+      <c r="P32" s="15">
+        <v>224.61599999999999</v>
+      </c>
+      <c r="Q32" s="15">
+        <v>228.24799999999999</v>
+      </c>
+      <c r="R32" s="15">
+        <v>229.471</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A33" s="9">
+        <v>2023</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="6">
+        <v>4</v>
+      </c>
+      <c r="F33" s="12">
+        <v>2.4010995370370371E-3</v>
+      </c>
+      <c r="G33">
+        <f>F33*86400</f>
+        <v>207.45500000000001</v>
+      </c>
+      <c r="I33">
+        <v>2016</v>
+      </c>
+      <c r="J33" t="s">
+        <v>38</v>
+      </c>
+      <c r="K33" s="15">
+        <v>207.46</v>
+      </c>
+      <c r="L33" s="15">
+        <v>208.56299999999999</v>
+      </c>
+      <c r="M33" s="15">
+        <v>212.60900000000001</v>
+      </c>
+      <c r="N33" s="15">
+        <v>213.298</v>
+      </c>
+      <c r="O33" s="15">
+        <v>213.471</v>
+      </c>
+      <c r="P33" s="15">
+        <v>214.89199999999997</v>
+      </c>
+      <c r="Q33" s="15">
+        <v>220.77</v>
+      </c>
+      <c r="R33" s="15">
+        <v>221.94</v>
+      </c>
+      <c r="S33" s="15">
+        <v>225.744</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A34" s="9">
+        <v>2024</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E34" s="6">
+        <v>4</v>
+      </c>
+      <c r="F34" s="14">
+        <v>2.4266666666666664E-3</v>
+      </c>
+      <c r="G34">
+        <f>F34*86400</f>
+        <v>209.66399999999999</v>
+      </c>
+      <c r="I34">
+        <v>2017</v>
+      </c>
+      <c r="J34" t="s">
+        <v>19</v>
+      </c>
+      <c r="K34" s="15">
+        <v>215.34100000000001</v>
+      </c>
+      <c r="L34" s="15">
+        <v>220.631</v>
+      </c>
+      <c r="M34" s="15">
+        <v>220.45099999999996</v>
+      </c>
+      <c r="N34" s="15">
+        <v>227.81</v>
+      </c>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="15"/>
+    </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A35" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="6">
+        <v>4</v>
+      </c>
+      <c r="F35" s="14">
+        <v>3.384212962962963E-3</v>
+      </c>
+      <c r="G35">
+        <f>F35*86400</f>
+        <v>292.39600000000002</v>
+      </c>
+      <c r="I35">
+        <v>2018</v>
+      </c>
+      <c r="J35" t="s">
+        <v>19</v>
+      </c>
+      <c r="K35" s="15">
+        <v>212.15100000000001</v>
+      </c>
+      <c r="L35" s="15">
+        <v>214.14900000000003</v>
+      </c>
+      <c r="M35" s="15">
+        <v>216.77599999999998</v>
+      </c>
+      <c r="N35" s="15">
+        <v>221.50900000000001</v>
+      </c>
+      <c r="O35" s="15">
+        <v>228.51599999999999</v>
+      </c>
+      <c r="P35" s="15">
+        <v>230.18600000000001</v>
+      </c>
+      <c r="Q35" s="15">
+        <v>233.17899999999997</v>
+      </c>
+      <c r="R35" s="15">
+        <v>245.09</v>
+      </c>
+      <c r="S35" s="15">
+        <v>264.36500000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A36" s="7">
+        <v>2019</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E36" s="8">
+        <v>5</v>
+      </c>
+      <c r="F36" s="11">
+        <v>2.5470698508435895E-3</v>
+      </c>
+      <c r="G36">
+        <f>F36*86400</f>
+        <v>220.06683511288614</v>
+      </c>
+      <c r="I36">
+        <v>2019</v>
+      </c>
+      <c r="J36" t="s">
+        <v>19</v>
+      </c>
+      <c r="K36">
+        <v>205.78876164707225</v>
+      </c>
+      <c r="L36">
+        <v>209.90029735875453</v>
+      </c>
+      <c r="M36">
+        <v>210.53862798994095</v>
+      </c>
+      <c r="N36">
+        <v>210.88807310786532</v>
+      </c>
+      <c r="O36">
+        <v>220.06683511288614</v>
+      </c>
+      <c r="P36">
+        <v>222.17650689158609</v>
+      </c>
+      <c r="Q36">
+        <v>222.68500381451162</v>
+      </c>
+      <c r="R36">
+        <v>223.02529685080023</v>
+      </c>
+      <c r="S36">
+        <v>227.03861758708405</v>
+      </c>
+      <c r="U36">
+        <f>K$43/K36</f>
+        <v>1.3251306719444447</v>
+      </c>
+      <c r="V36">
+        <f>L$43/L36</f>
+        <v>1.312670841666667</v>
+      </c>
+      <c r="W36">
+        <f>M$43/M36</f>
+        <v>1.3170884727777776</v>
+      </c>
+      <c r="X36">
+        <f>N$43/N36</f>
+        <v>1.3864985140740742</v>
+      </c>
+      <c r="Y36">
+        <f>O$43/O36</f>
+        <v>1.4390582744444445</v>
+      </c>
+      <c r="Z36">
+        <f>P$43/P36</f>
+        <v>1.4550503314814816</v>
+      </c>
+      <c r="AA36">
+        <f>Q$43/Q36</f>
+        <v>1.4981655445370372</v>
+      </c>
+      <c r="AB36">
+        <f>R$43/R36</f>
+        <v>1.5125683263888887</v>
+      </c>
+      <c r="AC36">
+        <f>S$43/S36</f>
+        <v>1.4998769972222219</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A37" s="7">
+        <v>2020</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E37" s="8">
+        <v>5</v>
+      </c>
+      <c r="F37" s="11">
+        <v>2.4823379629629631E-3</v>
+      </c>
+      <c r="G37">
+        <f>F37*86400</f>
+        <v>214.47400000000002</v>
+      </c>
+      <c r="I37">
+        <v>2020</v>
+      </c>
+      <c r="J37" t="s">
+        <v>19</v>
+      </c>
+      <c r="K37">
+        <v>200.81899999999999</v>
+      </c>
+      <c r="L37">
+        <v>207.358</v>
+      </c>
+      <c r="M37">
+        <v>209.10799999999998</v>
+      </c>
+      <c r="N37">
+        <v>210.625</v>
+      </c>
+      <c r="O37">
+        <v>214.47400000000002</v>
+      </c>
+      <c r="P37">
+        <v>215.14799999999997</v>
+      </c>
+      <c r="Q37">
+        <v>217.35399999999998</v>
+      </c>
+      <c r="R37">
+        <v>220.79400000000001</v>
+      </c>
+      <c r="S37">
+        <v>223.49699999999999</v>
+      </c>
+      <c r="U37">
+        <f>K$43/K37</f>
+        <v>1.3579242999915349</v>
+      </c>
+      <c r="V37">
+        <f>L$43/L37</f>
+        <v>1.3287647450303339</v>
+      </c>
+      <c r="W37">
+        <f>M$43/M37</f>
+        <v>1.3260994318725254</v>
+      </c>
+      <c r="X37">
+        <f>N$43/N37</f>
+        <v>1.3882302670623146</v>
+      </c>
+      <c r="Y37">
+        <f>O$43/O37</f>
+        <v>1.4765845743540009</v>
+      </c>
+      <c r="Z37">
+        <f>P$43/P37</f>
+        <v>1.5025842675739494</v>
+      </c>
+      <c r="AA37">
+        <f>Q$43/Q37</f>
+        <v>1.534910790691683</v>
+      </c>
+      <c r="AB37">
+        <f>R$43/R37</f>
+        <v>1.527854017772222</v>
+      </c>
+      <c r="AC37">
+        <f>S$43/S37</f>
+        <v>1.5236446126793648</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A38" s="7">
+        <v>2022</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E38" s="8">
+        <v>5</v>
+      </c>
+      <c r="F38" s="11">
+        <v>2.7122800925925925E-3</v>
+      </c>
+      <c r="G38">
+        <f>F38*86400</f>
+        <v>234.34099999999998</v>
+      </c>
+      <c r="I38">
+        <v>2021</v>
+      </c>
+      <c r="J38" t="s">
+        <v>38</v>
+      </c>
+      <c r="K38" s="15">
+        <v>199.483</v>
+      </c>
+      <c r="L38" s="15">
+        <v>199.946</v>
+      </c>
+      <c r="M38" s="15">
+        <v>205.41800000000001</v>
+      </c>
+      <c r="N38" s="15">
+        <v>206.483</v>
+      </c>
+      <c r="O38" s="15">
+        <v>212.62</v>
+      </c>
+      <c r="P38" s="15">
+        <v>233.45700000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A39" s="7">
+        <v>2023</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E39" s="8">
+        <v>5</v>
+      </c>
+      <c r="F39" s="11">
+        <v>2.4535648148148147E-3</v>
+      </c>
+      <c r="G39">
+        <f>F39*86400</f>
+        <v>211.988</v>
+      </c>
+      <c r="I39">
+        <v>2022</v>
+      </c>
+      <c r="J39" t="s">
+        <v>19</v>
+      </c>
+      <c r="K39">
+        <v>203.65600000000001</v>
+      </c>
+      <c r="L39">
+        <v>211.05799999999999</v>
+      </c>
+      <c r="M39">
+        <v>216.767</v>
+      </c>
+      <c r="N39">
+        <v>222.59899999999999</v>
+      </c>
+      <c r="O39">
+        <v>234.34099999999998</v>
+      </c>
+      <c r="P39">
+        <v>234.452</v>
+      </c>
+      <c r="Q39">
+        <v>235.70399999999998</v>
+      </c>
+      <c r="R39">
+        <v>237.5</v>
+      </c>
+      <c r="S39">
+        <v>239.06</v>
+      </c>
+      <c r="U39">
+        <f>K$43/K39</f>
+        <v>1.33900793494913</v>
+      </c>
+      <c r="V39">
+        <f>L$43/L39</f>
+        <v>1.3054705341659638</v>
+      </c>
+      <c r="W39">
+        <f>M$43/M39</f>
+        <v>1.2792445344540451</v>
+      </c>
+      <c r="X39">
+        <f>N$43/N39</f>
+        <v>1.3135548677217779</v>
+      </c>
+      <c r="Y39">
+        <f>O$43/O39</f>
+        <v>1.3514024434477965</v>
+      </c>
+      <c r="Z39">
+        <f>P$43/P39</f>
+        <v>1.3788664630713323</v>
+      </c>
+      <c r="AA39">
+        <f>Q$43/Q39</f>
+        <v>1.4154150969011983</v>
+      </c>
+      <c r="AB39">
+        <f>R$43/R39</f>
+        <v>1.4203831578947368</v>
+      </c>
+      <c r="AC39">
+        <f>S$43/S39</f>
+        <v>1.4244541119384253</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A40" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E40" s="8">
+        <v>5</v>
+      </c>
+      <c r="F40" s="13">
+        <v>2.4384953703703704E-3</v>
+      </c>
+      <c r="G40">
+        <f>F40*86400</f>
+        <v>210.68600000000001</v>
+      </c>
+      <c r="I40">
+        <v>2023</v>
+      </c>
+      <c r="J40" t="s">
+        <v>19</v>
+      </c>
+      <c r="K40">
+        <v>201.75900000000001</v>
+      </c>
+      <c r="L40">
+        <v>201.96299999999999</v>
+      </c>
+      <c r="M40">
+        <v>206.40199999999999</v>
+      </c>
+      <c r="N40">
+        <v>207.45500000000001</v>
+      </c>
+      <c r="O40">
+        <v>211.988</v>
+      </c>
+      <c r="P40">
+        <v>212.73400000000001</v>
+      </c>
+      <c r="Q40">
+        <v>215.46999999999997</v>
+      </c>
+      <c r="R40">
+        <v>217.577</v>
+      </c>
+      <c r="S40">
+        <v>217.64000000000004</v>
+      </c>
+      <c r="U40">
+        <f>K$43/K40</f>
+        <v>1.3515976982439444</v>
+      </c>
+      <c r="V40">
+        <f>L$43/L40</f>
+        <v>1.3642597901595837</v>
+      </c>
+      <c r="W40">
+        <f>M$43/M40</f>
+        <v>1.3434850437495762</v>
+      </c>
+      <c r="X40">
+        <f>N$43/N40</f>
+        <v>1.4094430117374852</v>
+      </c>
+      <c r="Y40">
+        <f>O$43/O40</f>
+        <v>1.493900598147065</v>
+      </c>
+      <c r="Z40">
+        <f>P$43/P40</f>
+        <v>1.519634849154343</v>
+      </c>
+      <c r="AA40">
+        <f>Q$43/Q40</f>
+        <v>1.5483315542766978</v>
+      </c>
+      <c r="AB40">
+        <f>R$43/R40</f>
+        <v>1.5504442105553438</v>
+      </c>
+      <c r="AC40">
+        <f>S$43/S40</f>
+        <v>1.5646480426392202</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A41" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="8">
+        <v>5</v>
+      </c>
+      <c r="F41" s="13">
+        <v>3.6653819444444446E-3</v>
+      </c>
+      <c r="G41">
+        <f>F41*86400</f>
+        <v>316.68900000000002</v>
+      </c>
+      <c r="I41">
+        <v>2024</v>
+      </c>
+      <c r="J41" t="s">
+        <v>19</v>
+      </c>
+      <c r="K41">
+        <v>205.37199999999999</v>
+      </c>
+      <c r="L41">
+        <v>205.94</v>
+      </c>
+      <c r="M41">
+        <v>208.69900000000001</v>
+      </c>
+      <c r="N41">
+        <v>209.66399999999999</v>
+      </c>
+      <c r="O41">
+        <v>210.68600000000001</v>
+      </c>
+      <c r="P41">
+        <v>211.43700000000001</v>
+      </c>
+      <c r="Q41">
+        <v>217.63900000000004</v>
+      </c>
+      <c r="R41">
+        <v>221.72200000000001</v>
+      </c>
+      <c r="S41">
+        <v>221.821</v>
+      </c>
+      <c r="U41">
+        <f>K$43/K41</f>
+        <v>1.3278197612137974</v>
+      </c>
+      <c r="V41">
+        <f>L$43/L41</f>
+        <v>1.3379139555210253</v>
+      </c>
+      <c r="W41">
+        <f>M$43/M41</f>
+        <v>1.3286982687986046</v>
+      </c>
+      <c r="X41">
+        <f>N$43/N41</f>
+        <v>1.3945932539682542</v>
+      </c>
+      <c r="Y41">
+        <f>O$43/O41</f>
+        <v>1.5031326239047682</v>
+      </c>
+      <c r="Z41">
+        <f>P$43/P41</f>
+        <v>1.5289566159186898</v>
+      </c>
+      <c r="AA41">
+        <f>Q$43/Q41</f>
+        <v>1.5329008128138797</v>
+      </c>
+      <c r="AB41">
+        <f>R$43/R41</f>
+        <v>1.5214593048953193</v>
+      </c>
+      <c r="AC41">
+        <f>S$43/S41</f>
+        <v>1.535156725467832</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A42" s="9">
+        <v>2019</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E42" s="6">
+        <v>6</v>
+      </c>
+      <c r="F42" s="12">
+        <v>2.5714873482822463E-3</v>
+      </c>
+      <c r="G42">
+        <f>F42*86400</f>
+        <v>222.17650689158609</v>
+      </c>
+      <c r="I42">
+        <v>2024</v>
+      </c>
+      <c r="J42" t="s">
+        <v>38</v>
+      </c>
+      <c r="K42">
+        <v>197.64299999999997</v>
+      </c>
+      <c r="L42">
+        <v>200.48</v>
+      </c>
+      <c r="M42">
+        <v>202.39</v>
+      </c>
+      <c r="N42">
+        <v>203.19199999999998</v>
+      </c>
+      <c r="O42">
+        <v>207.42</v>
+      </c>
+      <c r="P42">
+        <v>220.25900000000001</v>
+      </c>
+      <c r="Q42">
+        <v>226.29399999999998</v>
+      </c>
+      <c r="R42">
+        <v>229.029</v>
+      </c>
+      <c r="S42">
+        <v>236.59899999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A43" s="9">
+        <v>2020</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="6">
+        <v>6</v>
+      </c>
+      <c r="F43" s="12">
+        <v>2.4901388888888885E-3</v>
+      </c>
+      <c r="G43">
+        <f>F43*86400</f>
+        <v>215.14799999999997</v>
+      </c>
+      <c r="I43">
+        <v>2025</v>
+      </c>
+      <c r="J43" t="s">
+        <v>19</v>
+      </c>
+      <c r="K43">
+        <v>272.697</v>
+      </c>
+      <c r="L43">
+        <v>275.52999999999997</v>
+      </c>
+      <c r="M43">
+        <v>277.298</v>
+      </c>
+      <c r="N43">
+        <v>292.39600000000002</v>
+      </c>
+      <c r="O43">
+        <v>316.68900000000002</v>
+      </c>
+      <c r="P43">
+        <v>323.27800000000002</v>
+      </c>
+      <c r="Q43">
+        <v>333.61900000000003</v>
+      </c>
+      <c r="R43">
+        <v>337.34100000000001</v>
+      </c>
+      <c r="S43">
+        <v>340.53</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A44" s="9">
+        <v>2022</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="6">
+        <v>6</v>
+      </c>
+      <c r="F44" s="12">
+        <v>2.7135648148148149E-3</v>
+      </c>
+      <c r="G44">
+        <f>F44*86400</f>
+        <v>234.452</v>
+      </c>
+      <c r="U44">
+        <f>AVERAGE(U36:U41)</f>
+        <v>1.3402960732685703</v>
+      </c>
+      <c r="V44">
+        <f>AVERAGE(V36:V41)</f>
+        <v>1.3298159733087147</v>
+      </c>
+      <c r="W44">
+        <f>AVERAGE(W36:W41)</f>
+        <v>1.3189231503305057</v>
+      </c>
+      <c r="X44">
+        <f>AVERAGE(X36:X41)</f>
+        <v>1.3784639829127812</v>
+      </c>
+      <c r="Y44">
+        <f>AVERAGE(Y36:Y41)</f>
+        <v>1.4528157028596151</v>
+      </c>
+      <c r="Z44">
+        <f>AVERAGE(Z36:Z41)</f>
+        <v>1.4770185054399589</v>
+      </c>
+      <c r="AA44">
+        <f>AVERAGE(AA36:AA41)</f>
+        <v>1.5059447598440991</v>
+      </c>
+      <c r="AB44">
+        <f>AVERAGE(AB36:AB41)</f>
+        <v>1.5065418035013021</v>
+      </c>
+      <c r="AC44">
+        <f>AVERAGE(AC36:AC41)</f>
+        <v>1.5095560979894129</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A45" s="9">
+        <v>2023</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="6">
+        <v>6</v>
+      </c>
+      <c r="F45" s="12">
+        <v>2.4621990740740741E-3</v>
+      </c>
+      <c r="G45">
+        <f>F45*86400</f>
+        <v>212.73400000000001</v>
+      </c>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="16"/>
+      <c r="O45" s="16"/>
+      <c r="P45" s="16"/>
+      <c r="Q45" s="16"/>
+      <c r="R45" s="16"/>
+      <c r="S45" s="16"/>
+      <c r="T45" s="16"/>
+    </row>
+    <row r="46" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A46" s="9">
+        <v>2024</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E46" s="6">
+        <v>6</v>
+      </c>
+      <c r="F46" s="14">
+        <v>2.4471875000000001E-3</v>
+      </c>
+      <c r="G46">
+        <f>F46*86400</f>
+        <v>211.43700000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A47" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="6">
+        <v>6</v>
+      </c>
+      <c r="F47" s="14">
+        <v>3.7416435185185187E-3</v>
+      </c>
+      <c r="G47">
+        <f>F47*86400</f>
+        <v>323.27800000000002</v>
+      </c>
+      <c r="I47">
+        <f>6/16</f>
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="48" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A48" s="7">
+        <v>2019</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="8">
+        <v>7</v>
+      </c>
+      <c r="F48" s="11">
+        <v>2.5773727293346253E-3</v>
+      </c>
+      <c r="G48">
+        <f>F48*86400</f>
+        <v>222.68500381451162</v>
+      </c>
+      <c r="K48">
+        <f>K42/K41</f>
+        <v>0.96236585318349133</v>
+      </c>
+      <c r="L48">
+        <f>L42/L41</f>
+        <v>0.97348742352141393</v>
+      </c>
+      <c r="M48">
+        <f>M42/M41</f>
+        <v>0.96976985994182996</v>
+      </c>
+      <c r="N48">
+        <f>N42/N41</f>
+        <v>0.96913156288156288</v>
+      </c>
+      <c r="O48">
+        <f>O42/O41</f>
+        <v>0.98449825807125291</v>
+      </c>
+      <c r="P48">
+        <f>P42/P41</f>
+        <v>1.0417240123535616</v>
+      </c>
+      <c r="Q48">
+        <f>Q42/Q41</f>
+        <v>1.0397676886955001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A49" s="7">
+        <v>2020</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49" s="8">
+        <v>7</v>
+      </c>
+      <c r="F49" s="11">
+        <v>2.5156712962962962E-3</v>
+      </c>
+      <c r="G49">
+        <f>F49*86400</f>
+        <v>217.35399999999998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A50" s="7">
+        <v>2022</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E50" s="8">
+        <v>7</v>
+      </c>
+      <c r="F50" s="11">
+        <v>2.7280555555555552E-3</v>
+      </c>
+      <c r="G50">
+        <f>F50*86400</f>
+        <v>235.70399999999998</v>
+      </c>
+      <c r="T50">
+        <v>1</v>
+      </c>
+      <c r="U50">
+        <v>1.3402960732685703</v>
+      </c>
+    </row>
+    <row r="51" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A51" s="7">
+        <v>2023</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E51" s="8">
+        <v>7</v>
+      </c>
+      <c r="F51" s="11">
+        <v>2.4938657407407405E-3</v>
+      </c>
+      <c r="G51">
+        <f>F51*86400</f>
+        <v>215.46999999999997</v>
+      </c>
+      <c r="T51">
+        <v>2</v>
+      </c>
+      <c r="U51">
+        <v>1.3298159733087147</v>
+      </c>
+      <c r="W51">
+        <f>AVERAGE(U50:U52)</f>
+        <v>1.3296783989692635</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A52" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="8">
+        <v>7</v>
+      </c>
+      <c r="F52" s="13">
+        <v>2.5189699074074077E-3</v>
+      </c>
+      <c r="G52">
+        <f>F52*86400</f>
+        <v>217.63900000000004</v>
+      </c>
+      <c r="T52">
+        <v>3</v>
+      </c>
+      <c r="U52">
+        <v>1.3189231503305057</v>
+      </c>
+    </row>
+    <row r="53" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A53" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E53" s="8">
+        <v>7</v>
+      </c>
+      <c r="F53" s="13">
+        <v>3.8613310185185187E-3</v>
+      </c>
+      <c r="G53">
+        <f>F53*86400</f>
+        <v>333.61900000000003</v>
+      </c>
+      <c r="T53">
+        <v>4</v>
+      </c>
+      <c r="U53">
+        <v>1.3784639829127812</v>
+      </c>
+    </row>
+    <row r="54" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A54" s="9">
+        <v>2019</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E54" s="6">
+        <v>8</v>
+      </c>
+      <c r="F54" s="12">
+        <v>2.5813113061435213E-3</v>
+      </c>
+      <c r="G54">
+        <f>F54*86400</f>
+        <v>223.02529685080023</v>
+      </c>
+      <c r="I54" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="J54" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="T54">
+        <v>5</v>
+      </c>
+      <c r="U54">
+        <v>1.4528157028596151</v>
+      </c>
+    </row>
+    <row r="55" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A55" s="9">
+        <v>2020</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E55" s="6">
+        <v>8</v>
+      </c>
+      <c r="F55" s="12">
+        <v>2.5554861111111112E-3</v>
+      </c>
+      <c r="G55">
+        <f>F55*86400</f>
+        <v>220.79400000000001</v>
+      </c>
+      <c r="I55" s="17">
+        <v>2008</v>
+      </c>
+      <c r="J55" s="17">
+        <v>218.08500000000004</v>
+      </c>
+      <c r="K55">
+        <f>J55*1.33</f>
+        <v>290.05305000000004</v>
+      </c>
+      <c r="T55">
+        <v>6</v>
+      </c>
+      <c r="U55">
+        <v>1.4770185054399589</v>
+      </c>
+    </row>
+    <row r="56" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A56" s="9">
+        <v>2022</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E56" s="6">
+        <v>8</v>
+      </c>
+      <c r="F56" s="12">
+        <v>2.7488425925925927E-3</v>
+      </c>
+      <c r="G56">
+        <f>F56*86400</f>
+        <v>237.5</v>
+      </c>
+      <c r="I56" s="17">
+        <v>2012</v>
+      </c>
+      <c r="J56" s="17">
+        <v>211.52999999999997</v>
+      </c>
+      <c r="K56">
+        <f t="shared" ref="K56:K59" si="1">J56*1.33</f>
+        <v>281.3349</v>
+      </c>
+      <c r="T56">
+        <v>7</v>
+      </c>
+      <c r="U56">
+        <v>1.5059447598440991</v>
+      </c>
+    </row>
+    <row r="57" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A57" s="9">
+        <v>2023</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="6">
+        <v>8</v>
+      </c>
+      <c r="F57" s="12">
+        <v>2.5182523148148147E-3</v>
+      </c>
+      <c r="G57">
+        <f>F57*86400</f>
+        <v>217.577</v>
+      </c>
+      <c r="I57" s="17">
+        <v>2016</v>
+      </c>
+      <c r="J57" s="17">
+        <v>207.46</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="1"/>
+        <v>275.92180000000002</v>
+      </c>
+      <c r="T57">
+        <v>8</v>
+      </c>
+      <c r="U57">
+        <v>1.5065418035013021</v>
+      </c>
+    </row>
+    <row r="58" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A58" s="9">
+        <v>2024</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E58" s="6">
+        <v>8</v>
+      </c>
+      <c r="F58" s="14">
+        <v>2.5662268518518521E-3</v>
+      </c>
+      <c r="G58">
+        <f>F58*86400</f>
+        <v>221.72200000000001</v>
+      </c>
+      <c r="I58" s="17">
+        <v>2021</v>
+      </c>
+      <c r="J58" s="17">
+        <v>199.483</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="1"/>
+        <v>265.31238999999999</v>
+      </c>
+      <c r="T58">
+        <v>9</v>
+      </c>
+      <c r="U58">
+        <v>1.5095560979894129</v>
+      </c>
+    </row>
+    <row r="59" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A59" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="6">
+        <v>8</v>
+      </c>
+      <c r="F59" s="14">
+        <v>3.9044097222222223E-3</v>
+      </c>
+      <c r="G59">
+        <f>F59*86400</f>
+        <v>337.34100000000001</v>
+      </c>
+      <c r="I59" s="17">
+        <v>2024</v>
+      </c>
+      <c r="J59" s="17">
+        <v>197.64299999999997</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="1"/>
+        <v>262.86518999999998</v>
+      </c>
+    </row>
+    <row r="60" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A60" s="7">
+        <v>2019</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E60" s="8">
+        <v>9</v>
+      </c>
+      <c r="F60" s="11">
+        <v>2.6277617776282874E-3</v>
+      </c>
+      <c r="G60">
+        <f>F60*86400</f>
+        <v>227.03861758708405</v>
+      </c>
+      <c r="I60" t="s">
+        <v>39</v>
+      </c>
+      <c r="J60" cm="1">
+        <f t="array" ref="J60">TREND(J55:J59,I55:I59,2028,TRUE)</f>
+        <v>191.52528199052131</v>
+      </c>
+      <c r="K60">
+        <f>J60*1.33</f>
+        <v>254.72862504739336</v>
+      </c>
+    </row>
+    <row r="61" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A61" s="7">
+        <v>2020</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E61" s="8">
+        <v>9</v>
+      </c>
+      <c r="F61" s="11">
+        <v>2.5867708333333333E-3</v>
+      </c>
+      <c r="G61">
+        <f>F61*86400</f>
+        <v>223.49699999999999</v>
+      </c>
+      <c r="I61">
+        <v>2028</v>
+      </c>
+      <c r="J61" cm="1">
+        <f t="array" ref="J61">TREND(J55:J59,I55:I59,2028,TRUE)*W51</f>
+        <v>254.6670303192931</v>
+      </c>
+      <c r="K61" cm="1">
+        <f t="array" ref="K61">TREND(K55:K59,J55:J59,2028,TRUE)*X51</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A62" s="7">
+        <v>2022</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="8">
+        <v>9</v>
+      </c>
+      <c r="F62" s="11">
+        <v>2.7668981481481481E-3</v>
+      </c>
+      <c r="G62">
+        <f>F62*86400</f>
+        <v>239.06</v>
+      </c>
+      <c r="J62" s="1">
+        <f>J61/86400</f>
+        <v>2.9475350731399666E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A63" s="7">
+        <v>2023</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E63" s="8">
+        <v>9</v>
+      </c>
+      <c r="F63" s="11">
+        <v>2.5189814814814819E-3</v>
+      </c>
+      <c r="G63">
+        <f>F63*86400</f>
+        <v>217.64000000000004</v>
+      </c>
+      <c r="J63" cm="1">
+        <f t="array" ref="J63">TREND(J55:J59,I55:I59,2028,TRUE)*M97</f>
+        <v>251.68833237133805</v>
+      </c>
+      <c r="U63" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="V63" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="W63" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="X63" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z63" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB63" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC63" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="64" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A64" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E64" s="8">
+        <v>9</v>
+      </c>
+      <c r="F64" s="13">
+        <v>2.5673726851851851E-3</v>
+      </c>
+      <c r="G64">
+        <f>F64*86400</f>
+        <v>221.821</v>
+      </c>
+      <c r="J64" s="1">
+        <f>J63/86400</f>
+        <v>2.9130594024460422E-3</v>
+      </c>
+      <c r="U64" s="18">
+        <v>2016</v>
+      </c>
+      <c r="V64" s="20">
+        <v>211.69300000000001</v>
+      </c>
+      <c r="W64" s="20">
+        <v>215.47900000000001</v>
+      </c>
+      <c r="X64" s="20">
+        <v>215.78399999999996</v>
+      </c>
+      <c r="Z64" s="18">
+        <v>2016</v>
+      </c>
+      <c r="AA64" s="19">
+        <f>V$71/V64</f>
+        <v>1.2881720226932396</v>
+      </c>
+      <c r="AB64" s="19">
+        <f t="shared" ref="AB64:AC64" si="2">W$71/W64</f>
+        <v>1.27868609005982</v>
+      </c>
+      <c r="AC64" s="19">
+        <f t="shared" si="2"/>
+        <v>1.2850721091461834</v>
+      </c>
+    </row>
+    <row r="65" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A65" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E65" s="8">
+        <v>9</v>
+      </c>
+      <c r="F65" s="13">
+        <v>3.9413194444444443E-3</v>
+      </c>
+      <c r="G65">
+        <f>F65*86400</f>
+        <v>340.53</v>
+      </c>
+      <c r="U65" s="18">
+        <v>2018</v>
+      </c>
+      <c r="V65" s="20">
+        <v>212.15100000000001</v>
+      </c>
+      <c r="W65" s="20">
+        <v>214.14900000000003</v>
+      </c>
+      <c r="X65" s="20">
+        <v>216.77599999999998</v>
+      </c>
+      <c r="Z65" s="18">
+        <v>2018</v>
+      </c>
+      <c r="AA65" s="19">
+        <f t="shared" ref="AA65:AA70" si="3">V$71/V65</f>
+        <v>1.2853910657974743</v>
+      </c>
+      <c r="AB65" s="19">
+        <f t="shared" ref="AB65:AB70" si="4">W$71/W65</f>
+        <v>1.2866275350340182</v>
+      </c>
+      <c r="AC65" s="19">
+        <f t="shared" ref="AC65:AC70" si="5">X$71/X65</f>
+        <v>1.2791914234048052</v>
+      </c>
+    </row>
+    <row r="66" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A66" s="9">
+        <v>2019</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E66" s="6">
+        <v>10</v>
+      </c>
+      <c r="F66" s="12">
+        <v>2.645782622499736E-3</v>
+      </c>
+      <c r="G66">
+        <f>F66*86400</f>
+        <v>228.5956185839772</v>
+      </c>
+      <c r="U66" s="18">
+        <v>2019</v>
+      </c>
+      <c r="V66" s="20">
+        <v>205.78876164707225</v>
+      </c>
+      <c r="W66" s="20">
+        <v>209.90029735875453</v>
+      </c>
+      <c r="X66" s="20">
+        <v>210.53862798994095</v>
+      </c>
+      <c r="Z66" s="18">
+        <v>2019</v>
+      </c>
+      <c r="AA66" s="19">
+        <f t="shared" si="3"/>
+        <v>1.3251306719444447</v>
+      </c>
+      <c r="AB66" s="19">
+        <f t="shared" si="4"/>
+        <v>1.312670841666667</v>
+      </c>
+      <c r="AC66" s="19">
+        <f t="shared" si="5"/>
+        <v>1.3170884727777776</v>
+      </c>
+    </row>
+    <row r="67" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A67" s="9">
+        <v>2020</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E67" s="6">
+        <v>10</v>
+      </c>
+      <c r="F67" s="12">
+        <v>2.6236111111111113E-3</v>
+      </c>
+      <c r="G67">
+        <f>F67*86400</f>
+        <v>226.68</v>
+      </c>
+      <c r="U67" s="18">
+        <v>2020</v>
+      </c>
+      <c r="V67" s="20">
+        <v>200.81899999999999</v>
+      </c>
+      <c r="W67" s="20">
+        <v>207.358</v>
+      </c>
+      <c r="X67" s="20">
+        <v>209.10799999999998</v>
+      </c>
+      <c r="Z67" s="18">
+        <v>2020</v>
+      </c>
+      <c r="AA67" s="19">
+        <f>V$71/V67</f>
+        <v>1.3579242999915349</v>
+      </c>
+      <c r="AB67" s="19">
+        <f t="shared" si="4"/>
+        <v>1.3287647450303339</v>
+      </c>
+      <c r="AC67" s="19">
+        <f t="shared" si="5"/>
+        <v>1.3260994318725254</v>
+      </c>
+    </row>
+    <row r="68" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A68" s="9">
+        <v>2022</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E68" s="6">
+        <v>10</v>
+      </c>
+      <c r="F68" s="12">
+        <v>2.8624768518518517E-3</v>
+      </c>
+      <c r="G68">
+        <f>F68*86400</f>
+        <v>247.31799999999998</v>
+      </c>
+      <c r="I68" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="J68" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="U68" s="18">
+        <v>2022</v>
+      </c>
+      <c r="V68" s="20">
+        <v>203.65600000000001</v>
+      </c>
+      <c r="W68" s="20">
+        <v>211.05799999999999</v>
+      </c>
+      <c r="X68" s="20">
+        <v>216.767</v>
+      </c>
+      <c r="Z68" s="18">
+        <v>2022</v>
+      </c>
+      <c r="AA68" s="19">
+        <f t="shared" si="3"/>
+        <v>1.33900793494913</v>
+      </c>
+      <c r="AB68" s="19">
+        <f t="shared" si="4"/>
+        <v>1.3054705341659638</v>
+      </c>
+      <c r="AC68" s="19">
+        <f t="shared" si="5"/>
+        <v>1.2792445344540451</v>
+      </c>
+    </row>
+    <row r="69" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="A69" s="9">
+        <v>2023</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E69" s="6">
+        <v>10</v>
+      </c>
+      <c r="F69" s="12">
+        <v>2.6836342592592593E-3</v>
+      </c>
+      <c r="G69">
+        <f>F69*86400</f>
+        <v>231.86600000000001</v>
+      </c>
+      <c r="I69" s="17">
+        <v>2016</v>
+      </c>
+      <c r="J69" s="17">
+        <v>211.69300000000001</v>
+      </c>
+      <c r="U69" s="18">
+        <v>2023</v>
+      </c>
+      <c r="V69" s="20">
+        <v>201.75900000000001</v>
+      </c>
+      <c r="W69" s="20">
+        <v>201.96299999999999</v>
+      </c>
+      <c r="X69" s="20">
+        <v>206.40199999999999</v>
+      </c>
+      <c r="Z69" s="18">
+        <v>2023</v>
+      </c>
+      <c r="AA69" s="19">
+        <f t="shared" si="3"/>
+        <v>1.3515976982439444</v>
+      </c>
+      <c r="AB69" s="19">
+        <f t="shared" si="4"/>
+        <v>1.3642597901595837</v>
+      </c>
+      <c r="AC69" s="19">
+        <f t="shared" si="5"/>
+        <v>1.3434850437495762</v>
+      </c>
+    </row>
+    <row r="70" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="I70" s="17">
+        <v>2018</v>
+      </c>
+      <c r="J70" s="17">
+        <v>212.15100000000001</v>
+      </c>
+      <c r="U70" s="18">
+        <v>2024</v>
+      </c>
+      <c r="V70" s="20">
+        <v>205.37199999999999</v>
+      </c>
+      <c r="W70" s="20">
+        <v>205.94</v>
+      </c>
+      <c r="X70" s="20">
+        <v>208.69900000000001</v>
+      </c>
+      <c r="Z70" s="18">
+        <v>2024</v>
+      </c>
+      <c r="AA70" s="19">
+        <f t="shared" si="3"/>
+        <v>1.3278197612137974</v>
+      </c>
+      <c r="AB70" s="19">
+        <f t="shared" si="4"/>
+        <v>1.3379139555210253</v>
+      </c>
+      <c r="AC70" s="19">
+        <f t="shared" si="5"/>
+        <v>1.3286982687986046</v>
+      </c>
+    </row>
+    <row r="71" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="I71" s="17">
+        <v>2019</v>
+      </c>
+      <c r="J71" s="17">
+        <v>205.78876164707225</v>
+      </c>
+      <c r="U71" s="22">
+        <v>2025</v>
+      </c>
+      <c r="V71" s="21">
+        <v>272.697</v>
+      </c>
+      <c r="W71" s="21">
+        <v>275.52999999999997</v>
+      </c>
+      <c r="X71" s="21">
+        <v>277.298</v>
+      </c>
+      <c r="Z71" s="22">
+        <v>2025</v>
+      </c>
+      <c r="AA71" s="21">
+        <v>1</v>
+      </c>
+      <c r="AB71" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC71" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="I72" s="17">
+        <v>2020</v>
+      </c>
+      <c r="J72" s="17">
+        <v>200.81899999999999</v>
+      </c>
+      <c r="Z72" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA72" s="19">
+        <f>AVERAGE(AA66:AA70)</f>
+        <v>1.3402960732685703</v>
+      </c>
+      <c r="AB72" s="19">
+        <f t="shared" ref="AB72:AC72" si="6">AVERAGE(AB66:AB70)</f>
+        <v>1.3298159733087147</v>
+      </c>
+      <c r="AC72" s="19">
+        <f t="shared" si="6"/>
+        <v>1.3189231503305057</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="I73" s="17">
+        <v>2022</v>
+      </c>
+      <c r="J73" s="17">
+        <v>203.65600000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="I74" s="17">
+        <v>2023</v>
+      </c>
+      <c r="J74" s="17">
+        <v>201.75900000000001</v>
+      </c>
+    </row>
+    <row r="75" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="I75" s="17">
+        <v>2024</v>
+      </c>
+      <c r="J75" s="17">
+        <v>205.37199999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="Z79" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA79" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB79" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC79" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD79" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="80" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="Z80">
+        <v>2016</v>
+      </c>
+      <c r="AA80" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB80">
+        <v>1.2881720226932396</v>
+      </c>
+      <c r="AC80">
+        <v>1.27868609005982</v>
+      </c>
+      <c r="AD80">
+        <v>1.2850721091461834</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27 16384:16384" x14ac:dyDescent="0.45">
+      <c r="A81">
+        <v>2008</v>
+      </c>
+      <c r="B81">
+        <v>290.05305000000004</v>
+      </c>
+      <c r="AA81" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="82" spans="1:27 16384:16384" x14ac:dyDescent="0.45">
+      <c r="A82">
+        <v>2012</v>
+      </c>
+      <c r="B82">
+        <v>281.3349</v>
+      </c>
+    </row>
+    <row r="83" spans="1:27 16384:16384" x14ac:dyDescent="0.45">
+      <c r="A83">
+        <v>2016</v>
+      </c>
+      <c r="B83">
+        <v>275.92180000000002</v>
+      </c>
+    </row>
+    <row r="84" spans="1:27 16384:16384" x14ac:dyDescent="0.45">
+      <c r="A84">
+        <v>2021</v>
+      </c>
+      <c r="B84">
+        <v>265.31238999999999</v>
+      </c>
+    </row>
+    <row r="85" spans="1:27 16384:16384" x14ac:dyDescent="0.45">
+      <c r="A85">
+        <v>2024</v>
+      </c>
+      <c r="B85">
+        <v>262.86518999999998</v>
+      </c>
+      <c r="I85">
+        <v>2016</v>
+      </c>
+      <c r="L85">
+        <v>2020</v>
+      </c>
+      <c r="X85" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y85" s="18">
+        <v>1.31</v>
+      </c>
+      <c r="Z85" s="18">
+        <v>1.33</v>
+      </c>
+      <c r="AA85">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="86" spans="1:27 16384:16384" x14ac:dyDescent="0.45">
+      <c r="A86">
+        <v>2028</v>
+      </c>
+      <c r="B86">
+        <v>254.6670303192931</v>
+      </c>
+      <c r="I86" s="15">
+        <v>207.46</v>
+      </c>
+      <c r="J86" s="15">
+        <v>215.34100000000001</v>
+      </c>
+      <c r="K86">
+        <f>J86/I86</f>
+        <v>1.0379880458883641</v>
+      </c>
+      <c r="L86" s="15">
+        <v>199.483</v>
+      </c>
+      <c r="M86">
+        <v>203.65600000000001</v>
+      </c>
+      <c r="N86">
+        <f>M86/L86</f>
+        <v>1.0209190758109714</v>
+      </c>
+      <c r="X86" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y86" s="24">
+        <f>Y85*J60/86400</f>
+        <v>2.9039134190692469E-3</v>
+      </c>
+      <c r="Z86" s="25">
+        <f>Z85*J60/86400</f>
+        <v>2.9482479750855715E-3</v>
+      </c>
+      <c r="AA86" s="25">
+        <f>AA85*J60/86400</f>
+        <v>2.9704152530937332E-3</v>
+      </c>
+      <c r="XFD86" s="25">
+        <f>XFD85*XEN60/86400</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:27 16384:16384" x14ac:dyDescent="0.45">
+      <c r="I87" s="15">
+        <v>208.56299999999999</v>
+      </c>
+      <c r="J87" s="15">
+        <v>220.631</v>
+      </c>
+      <c r="K87">
+        <f t="shared" ref="K87:K89" si="7">J87/I87</f>
+        <v>1.0578626122562487</v>
+      </c>
+      <c r="L87" s="15">
+        <v>199.946</v>
+      </c>
+      <c r="M87">
+        <v>211.05799999999999</v>
+      </c>
+      <c r="N87">
+        <f t="shared" ref="N87:N91" si="8">M87/L87</f>
+        <v>1.0555750052514179</v>
+      </c>
+    </row>
+    <row r="88" spans="1:27 16384:16384" x14ac:dyDescent="0.45">
+      <c r="I88" s="15">
+        <v>213.471</v>
+      </c>
+      <c r="J88" s="15">
+        <v>220.45099999999996</v>
+      </c>
+      <c r="K88">
+        <f t="shared" si="7"/>
+        <v>1.0326976497978646</v>
+      </c>
+      <c r="L88" s="15">
+        <v>205.41800000000001</v>
+      </c>
+      <c r="M88">
+        <v>216.767</v>
+      </c>
+      <c r="N88">
+        <f t="shared" si="8"/>
+        <v>1.0552483229317782</v>
+      </c>
+    </row>
+    <row r="89" spans="1:27 16384:16384" x14ac:dyDescent="0.45">
+      <c r="I89" s="15">
+        <v>214.89199999999997</v>
+      </c>
+      <c r="J89" s="15">
+        <v>227.81</v>
+      </c>
+      <c r="K89">
+        <f t="shared" si="7"/>
+        <v>1.0601139176888859</v>
+      </c>
+      <c r="L89" s="15">
+        <v>206.483</v>
+      </c>
+      <c r="M89">
+        <v>222.59899999999999</v>
+      </c>
+      <c r="N89">
+        <f t="shared" si="8"/>
+        <v>1.0780500089595753</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27 16384:16384" x14ac:dyDescent="0.45">
+      <c r="K90">
+        <f>AVERAGE(K86:K89)</f>
+        <v>1.0471655564078408</v>
+      </c>
+      <c r="L90" s="15">
+        <v>212.62</v>
+      </c>
+      <c r="M90">
+        <v>234.34099999999998</v>
+      </c>
+      <c r="N90">
+        <f t="shared" si="8"/>
+        <v>1.1021587809237134</v>
+      </c>
+    </row>
+    <row r="91" spans="1:27 16384:16384" x14ac:dyDescent="0.45">
+      <c r="L91" s="15">
+        <v>233.45700000000002</v>
+      </c>
+      <c r="M91">
+        <v>234.452</v>
+      </c>
+      <c r="N91">
+        <f t="shared" si="8"/>
+        <v>1.0042620268400604</v>
+      </c>
+    </row>
+    <row r="92" spans="1:27 16384:16384" x14ac:dyDescent="0.45">
+      <c r="N92">
+        <f>AVERAGE(N86:N91)</f>
+        <v>1.0527022034529194</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27 16384:16384" x14ac:dyDescent="0.45">
+      <c r="N94">
+        <f>AVERAGE(N92,K90)</f>
+        <v>1.0499338799303801</v>
+      </c>
+    </row>
+    <row r="96" spans="1:27 16384:16384" x14ac:dyDescent="0.45">
+      <c r="L96" t="s">
+        <v>40</v>
+      </c>
+      <c r="M96">
+        <f>N94*K42</f>
+        <v>207.51208183108008</v>
+      </c>
+    </row>
+    <row r="97" spans="9:15" x14ac:dyDescent="0.45">
+      <c r="L97" t="s">
+        <v>41</v>
+      </c>
+      <c r="M97">
+        <f>K43/M96</f>
+        <v>1.3141258937490783</v>
+      </c>
+    </row>
+    <row r="100" spans="9:15" x14ac:dyDescent="0.45">
+      <c r="I100" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="J100" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="K100" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="L100" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="M100" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="N100" s="18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="101" spans="9:15" x14ac:dyDescent="0.45">
+      <c r="I101" s="34">
+        <v>2016</v>
+      </c>
+      <c r="J101" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="K101" s="31">
+        <v>211.69300000000001</v>
+      </c>
+      <c r="L101" s="31">
+        <v>215.47900000000001</v>
+      </c>
+      <c r="M101" s="31">
+        <v>215.78399999999996</v>
+      </c>
+      <c r="N101" s="31">
+        <v>215.92400000000001</v>
+      </c>
+    </row>
+    <row r="102" spans="9:15" x14ac:dyDescent="0.45">
+      <c r="I102" s="34">
+        <v>2016</v>
+      </c>
+      <c r="J102" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="K102" s="31">
+        <v>207.46</v>
+      </c>
+      <c r="L102" s="31">
+        <v>208.56299999999999</v>
+      </c>
+      <c r="M102" s="31">
+        <v>212.60900000000001</v>
+      </c>
+      <c r="N102" s="31">
+        <v>213.298</v>
+      </c>
+    </row>
+    <row r="103" spans="9:15" x14ac:dyDescent="0.45">
+      <c r="I103" s="35">
+        <v>2024</v>
+      </c>
+      <c r="J103" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="K103" s="33">
+        <v>205.37199999999999</v>
+      </c>
+      <c r="L103" s="33">
+        <v>205.94</v>
+      </c>
+      <c r="M103" s="33">
+        <v>208.69900000000001</v>
+      </c>
+      <c r="N103" s="33">
+        <v>209.66399999999999</v>
+      </c>
+    </row>
+    <row r="104" spans="9:15" x14ac:dyDescent="0.45">
+      <c r="I104" s="35">
+        <v>2024</v>
+      </c>
+      <c r="J104" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="K104" s="33">
+        <v>197.64299999999997</v>
+      </c>
+      <c r="L104" s="33">
+        <v>200.48</v>
+      </c>
+      <c r="M104" s="33">
+        <v>202.39</v>
+      </c>
+      <c r="N104" s="33">
+        <v>203.19199999999998</v>
+      </c>
+    </row>
+    <row r="105" spans="9:15" x14ac:dyDescent="0.45">
+      <c r="K105" s="29">
+        <f>K101/K102</f>
+        <v>1.0204039332883448</v>
+      </c>
+      <c r="L105" s="29">
+        <f>L101/L102</f>
+        <v>1.0331602441468526</v>
+      </c>
+      <c r="M105" s="29">
+        <f>M101/M102</f>
+        <v>1.0149335164550888</v>
+      </c>
+      <c r="N105" s="29">
+        <f>N101/N102</f>
+        <v>1.0123114140779568</v>
+      </c>
+      <c r="O105" s="28">
+        <f>AVERAGE(K105:N105)</f>
+        <v>1.0202022769920607</v>
+      </c>
+    </row>
+    <row r="106" spans="9:15" x14ac:dyDescent="0.45">
+      <c r="K106" s="29">
+        <f>K103/K104</f>
+        <v>1.0391058625906306</v>
+      </c>
+      <c r="L106" s="29">
+        <f>L103/L104</f>
+        <v>1.0272346368715084</v>
+      </c>
+      <c r="M106" s="29">
+        <f>M103/M104</f>
+        <v>1.0311724887593261</v>
+      </c>
+      <c r="N106" s="29">
+        <f>N103/N104</f>
+        <v>1.0318516477026656</v>
+      </c>
+      <c r="O106" s="28">
+        <f>AVERAGE(K106:N106)</f>
+        <v>1.0323411589810327</v>
+      </c>
+    </row>
+    <row r="107" spans="9:15" x14ac:dyDescent="0.45">
+      <c r="K107" s="27"/>
+      <c r="L107" s="27"/>
+      <c r="M107" s="27"/>
+      <c r="N107" s="27"/>
+    </row>
+    <row r="108" spans="9:15" x14ac:dyDescent="0.45">
+      <c r="J108" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="K108" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="L108" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="M108" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="N108" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="O108" s="37" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="109" spans="9:15" x14ac:dyDescent="0.45">
+      <c r="J109" s="18">
+        <v>2016</v>
+      </c>
+      <c r="K109" s="36">
+        <f>(K101-K102)/K101</f>
+        <v>1.9995937513285766E-2</v>
+      </c>
+      <c r="L109" s="36">
+        <f t="shared" ref="L109:N111" si="9">(L101-L102)/L101</f>
+        <v>3.2095935102724744E-2</v>
+      </c>
+      <c r="M109" s="36">
+        <f t="shared" si="9"/>
+        <v>1.4713787861935801E-2</v>
+      </c>
+      <c r="N109" s="36">
+        <f t="shared" si="9"/>
+        <v>1.2161686519330897E-2</v>
+      </c>
+      <c r="O109" s="38">
+        <f>AVERAGE(K109:N109)</f>
+        <v>1.9741836749319303E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="9:15" x14ac:dyDescent="0.45">
+      <c r="J110" s="18">
+        <v>2024</v>
+      </c>
+      <c r="K110" s="36">
+        <v>3.7634146816508646E-2</v>
+      </c>
+      <c r="L110" s="36">
+        <v>2.6512576478586035E-2</v>
+      </c>
+      <c r="M110" s="36">
+        <v>3.0230140058170023E-2</v>
+      </c>
+      <c r="N110" s="36">
+        <v>3.0868437118437161E-2</v>
+      </c>
+      <c r="O110" s="38">
+        <f>AVERAGE(K110:N110)</f>
+        <v>3.1311325117925469E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="9:15" x14ac:dyDescent="0.45">
+      <c r="K111" s="26"/>
+      <c r="L111" s="26"/>
+      <c r="M111" s="26"/>
+      <c r="N111" s="26"/>
+    </row>
+    <row r="115" spans="10:17" x14ac:dyDescent="0.45">
+      <c r="J115" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="K115" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="L115" s="18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="116" spans="10:17" x14ac:dyDescent="0.45">
+      <c r="J116" s="40">
+        <f>O109</f>
+        <v>1.9741836749319303E-2</v>
+      </c>
+      <c r="K116" s="39">
+        <f>Y86</f>
+        <v>2.9039134190692469E-3</v>
+      </c>
+      <c r="L116" s="39">
+        <f>K116/(1-J116)</f>
+        <v>2.9623965685115455E-3</v>
+      </c>
+    </row>
+    <row r="117" spans="10:17" x14ac:dyDescent="0.45">
+      <c r="J117" s="40">
+        <v>1.9741836749319303E-2</v>
+      </c>
+      <c r="K117" s="39">
+        <f>Z86</f>
+        <v>2.9482479750855715E-3</v>
+      </c>
+      <c r="L117" s="39">
+        <f t="shared" ref="L117:L119" si="10">K117/(1-J117)</f>
+        <v>3.0076239970384397E-3</v>
+      </c>
+      <c r="O117">
+        <f>35.53-19.5</f>
+        <v>16.03</v>
+      </c>
+      <c r="P117">
+        <f>O117/3</f>
+        <v>5.3433333333333337</v>
+      </c>
+      <c r="Q117">
+        <f>P117/16</f>
+        <v>0.33395833333333336</v>
+      </c>
+    </row>
+    <row r="118" spans="10:17" x14ac:dyDescent="0.45">
+      <c r="J118" s="40">
+        <f>O110</f>
+        <v>3.1311325117925469E-2</v>
+      </c>
+      <c r="K118" s="39">
+        <f>K116</f>
+        <v>2.9039134190692469E-3</v>
+      </c>
+      <c r="L118" s="39">
+        <f t="shared" si="10"/>
+        <v>2.9977778148616852E-3</v>
+      </c>
+    </row>
+    <row r="119" spans="10:17" x14ac:dyDescent="0.45">
+      <c r="J119" s="40">
+        <v>3.1311325117925469E-2</v>
+      </c>
+      <c r="K119" s="39">
+        <f>K117</f>
+        <v>2.9482479750855715E-3</v>
+      </c>
+      <c r="L119" s="39">
+        <f t="shared" si="10"/>
+        <v>3.0435454150885815E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="10:17" x14ac:dyDescent="0.45">
+      <c r="K122" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L122" s="17">
+        <v>2025</v>
+      </c>
+      <c r="M122" s="17">
+        <v>2025</v>
+      </c>
+      <c r="N122" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="O122" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="123" spans="10:17" x14ac:dyDescent="0.45">
+      <c r="K123" s="23">
+        <v>3.1890046296296293E-3</v>
+      </c>
+      <c r="L123" s="23">
+        <v>3.1271604938271596E-3</v>
+      </c>
+      <c r="M123" s="23">
+        <v>3.0653163580246904E-3</v>
+      </c>
+      <c r="N123" s="23">
+        <v>3.0034722222222207E-3</v>
+      </c>
+      <c r="O123" s="17"/>
+    </row>
+    <row r="124" spans="10:17" x14ac:dyDescent="0.45">
+      <c r="K124" s="1"/>
+      <c r="L124" s="1"/>
+      <c r="M124" s="1"/>
+      <c r="N124" s="1"/>
+    </row>
+    <row r="125" spans="10:17" x14ac:dyDescent="0.45">
+      <c r="K125" s="23">
+        <v>3.1890046296296293E-3</v>
+      </c>
+    </row>
+    <row r="126" spans="10:17" x14ac:dyDescent="0.45">
+      <c r="K126" s="33">
+        <f>K125*86400</f>
+        <v>275.52999999999997</v>
+      </c>
+      <c r="L126" s="2">
+        <f>K126-P117</f>
+        <v>270.18666666666661</v>
+      </c>
+      <c r="M126" s="2">
+        <f>L126-P117</f>
+        <v>264.84333333333325</v>
+      </c>
+      <c r="N126" s="2">
+        <f>M126-P117</f>
+        <v>259.49999999999989</v>
+      </c>
+    </row>
+    <row r="127" spans="10:17" x14ac:dyDescent="0.45">
+      <c r="K127" s="23">
+        <f>K126/86400</f>
+        <v>3.1890046296296293E-3</v>
+      </c>
+      <c r="L127" s="23">
+        <f t="shared" ref="L127:N127" si="11">L126/86400</f>
+        <v>3.1271604938271596E-3</v>
+      </c>
+      <c r="M127" s="23">
+        <f t="shared" si="11"/>
+        <v>3.0653163580246904E-3</v>
+      </c>
+      <c r="N127" s="23">
+        <f t="shared" si="11"/>
+        <v>3.0034722222222207E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A11:G23" xr:uid="{ECED1680-AA5F-4E5A-A3DB-8DB035FF2C31}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A12:G70">
+      <sortCondition ref="E11:E23"/>
+    </sortState>
+  </autoFilter>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A1:B5">
+    <cfRule type="expression" dxfId="14" priority="21">
+      <formula>$F1&lt;4</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="22">
+      <formula>$F1&gt;6</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="23">
+      <formula>$F1&gt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A6">
+    <cfRule type="expression" dxfId="11" priority="18">
+      <formula>$F6&lt;4</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="19">
+      <formula>$F6&gt;6</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="20">
+      <formula>$F6&gt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="8" priority="15">
+      <formula>$F6&lt;4</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="16">
+      <formula>$F6&gt;6</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="17">
+      <formula>$F6&gt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A52:A61 A12:F51 A62:C69 D52:E69">
+    <cfRule type="expression" dxfId="5" priority="12">
+      <formula>$E12&lt;4</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="13">
+      <formula>$E12&gt;6</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="14">
+      <formula>$E12&gt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52:C61">
+    <cfRule type="expression" dxfId="2" priority="9">
+      <formula>$E52&lt;4</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="10">
+      <formula>$E52&gt;6</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="11">
+      <formula>$E52&gt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA64:AC70">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L116:L119">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K116:K119">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>